--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD623158-3B67-4F6F-A420-ADAF181AFB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31A773C-8B7C-4BA4-8328-3486E17F3EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -327,6 +327,21 @@
   <si>
     <t>Executed</t>
   </si>
+  <si>
+    <t>Risen Mnawan</t>
+  </si>
+  <si>
+    <t>Risen Shadbagh</t>
+  </si>
+  <si>
+    <t>Vip</t>
+  </si>
+  <si>
+    <t>Umaima Paragon</t>
+  </si>
+  <si>
+    <t>On The Way</t>
+  </si>
 </sst>
 </file>
 
@@ -1580,102 +1595,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1690,6 +1609,102 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2225,14 +2240,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="139">
+      <c r="B1" s="149">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
-      </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
+        <v>46205</v>
+      </c>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2254,10 +2269,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="171" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="150" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2290,13 +2305,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="153"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="156" t="s">
+      <c r="M2" s="163"/>
+      <c r="N2" s="164"/>
+      <c r="O2" s="165"/>
+      <c r="P2" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="157"/>
+      <c r="Q2" s="167"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2315,8 +2330,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="161"/>
-      <c r="B3" s="141"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="151"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2347,29 +2362,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="158" t="s">
+      <c r="M3" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="159"/>
-      <c r="O3" s="160"/>
+      <c r="N3" s="169"/>
+      <c r="O3" s="170"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="143" t="s">
+      <c r="R3" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="144"/>
-      <c r="T3" s="144"/>
-      <c r="U3" s="145"/>
-      <c r="V3" s="146" t="s">
+      <c r="S3" s="154"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="155"/>
+      <c r="V3" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="147"/>
-      <c r="X3" s="147"/>
-      <c r="Y3" s="148"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="157"/>
+      <c r="Y3" s="158"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="161"/>
-      <c r="B4" s="142"/>
+      <c r="A4" s="171"/>
+      <c r="B4" s="152"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2447,26 +2462,26 @@
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="171" t="s">
+      <c r="C5" s="139" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="172"/>
-      <c r="E5" s="173"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="141"/>
       <c r="F5" s="46"/>
-      <c r="G5" s="174">
+      <c r="G5" s="142">
         <v>40</v>
       </c>
-      <c r="H5" s="173">
+      <c r="H5" s="141">
         <v>40</v>
       </c>
       <c r="I5" s="46"/>
-      <c r="J5" s="174">
+      <c r="J5" s="142">
         <v>40</v>
       </c>
-      <c r="K5" s="173">
+      <c r="K5" s="141">
         <v>40</v>
       </c>
-      <c r="L5" s="175">
+      <c r="L5" s="143">
         <v>40</v>
       </c>
       <c r="M5" s="37">
@@ -2529,26 +2544,26 @@
       <c r="B6" s="47">
         <v>2</v>
       </c>
-      <c r="C6" s="176" t="s">
+      <c r="C6" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="177"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="180">
+      <c r="D6" s="145"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="148">
         <v>80</v>
       </c>
-      <c r="H6" s="178">
+      <c r="H6" s="146">
         <v>80</v>
       </c>
       <c r="I6" s="56"/>
-      <c r="J6" s="180">
+      <c r="J6" s="148">
         <v>80</v>
       </c>
-      <c r="K6" s="178">
+      <c r="K6" s="146">
         <v>80</v>
       </c>
-      <c r="L6" s="179">
+      <c r="L6" s="147">
         <v>80</v>
       </c>
       <c r="M6" s="48">
@@ -2611,26 +2626,26 @@
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="176" t="s">
+      <c r="C7" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="177"/>
-      <c r="E7" s="178"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="180">
+      <c r="D7" s="145"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="148">
         <v>40</v>
       </c>
-      <c r="H7" s="178">
+      <c r="H7" s="146">
         <v>40</v>
       </c>
       <c r="I7" s="56"/>
-      <c r="J7" s="180">
+      <c r="J7" s="148">
         <v>40</v>
       </c>
-      <c r="K7" s="178">
+      <c r="K7" s="146">
         <v>40</v>
       </c>
-      <c r="L7" s="179">
+      <c r="L7" s="147">
         <v>40</v>
       </c>
       <c r="M7" s="48">
@@ -2693,26 +2708,26 @@
       <c r="B8" s="47">
         <v>4</v>
       </c>
-      <c r="C8" s="176" t="s">
+      <c r="C8" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="177"/>
-      <c r="E8" s="178"/>
-      <c r="F8" s="179"/>
-      <c r="G8" s="180">
+      <c r="D8" s="145"/>
+      <c r="E8" s="146"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="148">
         <v>40</v>
       </c>
-      <c r="H8" s="178">
+      <c r="H8" s="146">
         <v>40</v>
       </c>
       <c r="I8" s="56"/>
-      <c r="J8" s="180">
+      <c r="J8" s="148">
         <v>40</v>
       </c>
-      <c r="K8" s="178">
+      <c r="K8" s="146">
         <v>40</v>
       </c>
-      <c r="L8" s="179">
+      <c r="L8" s="147">
         <v>40</v>
       </c>
       <c r="M8" s="48">
@@ -2775,26 +2790,26 @@
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="176" t="s">
+      <c r="C9" s="144" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="177"/>
-      <c r="E9" s="178"/>
-      <c r="F9" s="179"/>
-      <c r="G9" s="180">
+      <c r="D9" s="145"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="148">
         <v>40</v>
       </c>
-      <c r="H9" s="178">
+      <c r="H9" s="146">
         <v>40</v>
       </c>
       <c r="I9" s="56"/>
-      <c r="J9" s="180">
+      <c r="J9" s="148">
         <v>40</v>
       </c>
-      <c r="K9" s="178">
+      <c r="K9" s="146">
         <v>40</v>
       </c>
-      <c r="L9" s="179">
+      <c r="L9" s="147">
         <v>40</v>
       </c>
       <c r="M9" s="48">
@@ -2857,26 +2872,26 @@
       <c r="B10" s="47">
         <v>6</v>
       </c>
-      <c r="C10" s="176" t="s">
+      <c r="C10" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="177"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="180">
+      <c r="D10" s="145"/>
+      <c r="E10" s="146"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="148">
         <v>40</v>
       </c>
-      <c r="H10" s="178">
+      <c r="H10" s="146">
         <v>40</v>
       </c>
       <c r="I10" s="56"/>
-      <c r="J10" s="180">
+      <c r="J10" s="148">
         <v>40</v>
       </c>
-      <c r="K10" s="178">
+      <c r="K10" s="146">
         <v>40</v>
       </c>
-      <c r="L10" s="179">
+      <c r="L10" s="147">
         <v>40</v>
       </c>
       <c r="M10" s="48">
@@ -2939,26 +2954,26 @@
       <c r="B11" s="47">
         <v>7</v>
       </c>
-      <c r="C11" s="176" t="s">
+      <c r="C11" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="177"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="180">
+      <c r="D11" s="145"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148">
         <v>40</v>
       </c>
-      <c r="H11" s="178">
+      <c r="H11" s="146">
         <v>40</v>
       </c>
       <c r="I11" s="56"/>
-      <c r="J11" s="180">
+      <c r="J11" s="148">
         <v>40</v>
       </c>
-      <c r="K11" s="178">
+      <c r="K11" s="146">
         <v>40</v>
       </c>
-      <c r="L11" s="179">
+      <c r="L11" s="147">
         <v>40</v>
       </c>
       <c r="M11" s="48">
@@ -3021,26 +3036,26 @@
       <c r="B12" s="47">
         <v>8</v>
       </c>
-      <c r="C12" s="176" t="s">
+      <c r="C12" s="144" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="177"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="180">
+      <c r="D12" s="145"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="148">
         <v>40</v>
       </c>
-      <c r="H12" s="178">
+      <c r="H12" s="146">
         <v>40</v>
       </c>
       <c r="I12" s="56"/>
-      <c r="J12" s="180">
+      <c r="J12" s="148">
         <v>40</v>
       </c>
-      <c r="K12" s="178">
+      <c r="K12" s="146">
         <v>40</v>
       </c>
-      <c r="L12" s="179">
+      <c r="L12" s="147">
         <v>40</v>
       </c>
       <c r="M12" s="48">
@@ -3103,26 +3118,26 @@
       <c r="B13" s="47">
         <v>9</v>
       </c>
-      <c r="C13" s="176" t="s">
+      <c r="C13" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="177"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="180">
+      <c r="D13" s="145"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="147"/>
+      <c r="G13" s="148">
         <v>40</v>
       </c>
-      <c r="H13" s="178">
+      <c r="H13" s="146">
         <v>40</v>
       </c>
       <c r="I13" s="56"/>
-      <c r="J13" s="180">
+      <c r="J13" s="148">
         <v>40</v>
       </c>
-      <c r="K13" s="178">
+      <c r="K13" s="146">
         <v>40</v>
       </c>
-      <c r="L13" s="179">
+      <c r="L13" s="147">
         <v>40</v>
       </c>
       <c r="M13" s="48">
@@ -3185,26 +3200,26 @@
       <c r="B14" s="47">
         <v>10</v>
       </c>
-      <c r="C14" s="176" t="s">
+      <c r="C14" s="144" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="177"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="180">
+      <c r="D14" s="145"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="147"/>
+      <c r="G14" s="148">
         <v>40</v>
       </c>
-      <c r="H14" s="178">
+      <c r="H14" s="146">
         <v>40</v>
       </c>
       <c r="I14" s="56"/>
-      <c r="J14" s="180">
+      <c r="J14" s="148">
         <v>40</v>
       </c>
-      <c r="K14" s="178">
+      <c r="K14" s="146">
         <v>40</v>
       </c>
-      <c r="L14" s="179">
+      <c r="L14" s="147">
         <v>40</v>
       </c>
       <c r="M14" s="48">
@@ -3267,26 +3282,26 @@
       <c r="B15" s="47">
         <v>11</v>
       </c>
-      <c r="C15" s="176" t="s">
+      <c r="C15" s="144" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="177"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="180">
+      <c r="D15" s="145"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="147"/>
+      <c r="G15" s="148">
         <v>40</v>
       </c>
-      <c r="H15" s="178">
+      <c r="H15" s="146">
         <v>40</v>
       </c>
       <c r="I15" s="56"/>
-      <c r="J15" s="180">
+      <c r="J15" s="148">
         <v>40</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="146">
         <v>40</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="147">
         <v>40</v>
       </c>
       <c r="M15" s="48">
@@ -3349,26 +3364,26 @@
       <c r="B16" s="47">
         <v>12</v>
       </c>
-      <c r="C16" s="176" t="s">
+      <c r="C16" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="177"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="180">
+      <c r="D16" s="145"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="148">
         <v>40</v>
       </c>
-      <c r="H16" s="178">
+      <c r="H16" s="146">
         <v>40</v>
       </c>
       <c r="I16" s="56"/>
-      <c r="J16" s="180">
+      <c r="J16" s="148">
         <v>40</v>
       </c>
-      <c r="K16" s="178">
+      <c r="K16" s="146">
         <v>40</v>
       </c>
-      <c r="L16" s="179">
+      <c r="L16" s="147">
         <v>40</v>
       </c>
       <c r="M16" s="48">
@@ -3431,26 +3446,26 @@
       <c r="B17" s="47">
         <v>13</v>
       </c>
-      <c r="C17" s="176" t="s">
+      <c r="C17" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="177"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="180">
+      <c r="D17" s="145"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="148">
         <v>40</v>
       </c>
-      <c r="H17" s="178">
+      <c r="H17" s="146">
         <v>40</v>
       </c>
       <c r="I17" s="56"/>
-      <c r="J17" s="180">
+      <c r="J17" s="148">
         <v>40</v>
       </c>
-      <c r="K17" s="178">
+      <c r="K17" s="146">
         <v>40</v>
       </c>
-      <c r="L17" s="179">
+      <c r="L17" s="147">
         <v>40</v>
       </c>
       <c r="M17" s="48">
@@ -10992,10 +11007,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="149" t="s">
+      <c r="B132" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="150"/>
+      <c r="C132" s="160"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11259,10 +11274,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="162" t="s">
+      <c r="B136" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="163"/>
+      <c r="C136" s="173"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11353,10 +11368,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="151" t="s">
+      <c r="B137" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="152"/>
+      <c r="C137" s="162"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11488,24 +11503,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="165"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="168" t="s">
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="176"/>
+      <c r="H3" s="178" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="169"/>
-      <c r="K3" s="170" t="s">
+      <c r="I3" s="179"/>
+      <c r="K3" s="180" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="170"/>
-      <c r="M3" s="170"/>
-      <c r="N3" s="170"/>
-      <c r="O3" s="170"/>
+      <c r="L3" s="180"/>
+      <c r="M3" s="180"/>
+      <c r="N3" s="180"/>
+      <c r="O3" s="180"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -11547,17 +11562,21 @@
       <c r="C5" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="79"/>
+      <c r="D5" s="92">
+        <v>35.85</v>
+      </c>
+      <c r="E5" s="79">
+        <v>70</v>
+      </c>
       <c r="F5" s="79"/>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>0</v>
+        <v>105.85</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>0</v>
+        <v>105.85</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11578,11 +11597,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>0</v>
+        <v>1434</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -11590,7 +11609,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>0</v>
+        <v>4234</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11598,7 +11617,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>0</v>
+        <v>4234</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11651,11 +11670,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>0</v>
+        <v>-35.85</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -11685,14 +11704,14 @@
       <c r="O10" s="81"/>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="177" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="167"/>
-      <c r="F11" s="167" t="s">
+      <c r="D11" s="177"/>
+      <c r="F11" s="177" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="167"/>
+      <c r="G11" s="177"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -11718,7 +11737,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>3434</v>
+        <v>3539.85</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11750,7 +11769,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>137360</v>
+        <v>141594</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12004,36 +12023,60 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
+      <c r="I3" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="81">
+        <v>10</v>
+      </c>
+      <c r="K3" s="81" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
+      <c r="I4" s="81" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="81">
+        <v>9</v>
+      </c>
+      <c r="K4" s="81" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
+      <c r="I5" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="81">
+        <v>18</v>
+      </c>
+      <c r="K5" s="81" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
+      <c r="I6" s="81" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" s="81">
+        <v>5</v>
+      </c>
+      <c r="K6" s="81" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31A773C-8B7C-4BA4-8328-3486E17F3EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5457CF98-FD11-44C8-A765-8B9375118901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="114">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -340,7 +340,31 @@
     <t>Umaima Paragon</t>
   </si>
   <si>
-    <t>On The Way</t>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Raheem Store</t>
+  </si>
+  <si>
+    <t>Clinix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Model </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Shadra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">On the way </t>
+  </si>
+  <si>
+    <t>Manawan (Risen)</t>
+  </si>
+  <si>
+    <t>Shadbagh (Risen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umaima  paragon City </t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1259,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1595,20 +1619,45 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1645,45 +1694,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1704,6 +1714,39 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2240,14 +2283,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="149">
+      <c r="B1" s="152">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
-      </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
+        <v>46206</v>
+      </c>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2269,10 +2312,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="153" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2305,13 +2348,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="163"/>
-      <c r="N2" s="164"/>
-      <c r="O2" s="165"/>
-      <c r="P2" s="166" t="s">
+      <c r="M2" s="141"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="143"/>
+      <c r="P2" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="167"/>
+      <c r="Q2" s="145"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2330,8 +2373,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="171"/>
-      <c r="B3" s="151"/>
+      <c r="A3" s="149"/>
+      <c r="B3" s="154"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2362,29 +2405,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="168" t="s">
+      <c r="M3" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="169"/>
-      <c r="O3" s="170"/>
+      <c r="N3" s="147"/>
+      <c r="O3" s="148"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="153" t="s">
+      <c r="R3" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="154"/>
-      <c r="T3" s="154"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="156" t="s">
+      <c r="S3" s="157"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="157"/>
-      <c r="X3" s="157"/>
-      <c r="Y3" s="158"/>
+      <c r="W3" s="160"/>
+      <c r="X3" s="160"/>
+      <c r="Y3" s="161"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="171"/>
-      <c r="B4" s="152"/>
+      <c r="A4" s="149"/>
+      <c r="B4" s="155"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -2462,26 +2505,26 @@
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="C5" s="172" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="140"/>
-      <c r="E5" s="141"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="142">
+      <c r="D5" s="173"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="176">
         <v>40</v>
       </c>
-      <c r="H5" s="141">
+      <c r="H5" s="174">
         <v>40</v>
       </c>
-      <c r="I5" s="46"/>
-      <c r="J5" s="142">
+      <c r="I5" s="175"/>
+      <c r="J5" s="176">
         <v>40</v>
       </c>
-      <c r="K5" s="141">
+      <c r="K5" s="174">
         <v>40</v>
       </c>
-      <c r="L5" s="143">
+      <c r="L5" s="177">
         <v>40</v>
       </c>
       <c r="M5" s="37">
@@ -2544,26 +2587,26 @@
       <c r="B6" s="47">
         <v>2</v>
       </c>
-      <c r="C6" s="144" t="s">
+      <c r="C6" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="145"/>
-      <c r="E6" s="146"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="148">
+      <c r="D6" s="179"/>
+      <c r="E6" s="180"/>
+      <c r="F6" s="181"/>
+      <c r="G6" s="182">
         <v>80</v>
       </c>
-      <c r="H6" s="146">
+      <c r="H6" s="180">
         <v>80</v>
       </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="148">
+      <c r="I6" s="183"/>
+      <c r="J6" s="182">
         <v>80</v>
       </c>
-      <c r="K6" s="146">
+      <c r="K6" s="180">
         <v>80</v>
       </c>
-      <c r="L6" s="147">
+      <c r="L6" s="181">
         <v>80</v>
       </c>
       <c r="M6" s="48">
@@ -2626,26 +2669,26 @@
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="145"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="148">
+      <c r="D7" s="179"/>
+      <c r="E7" s="180"/>
+      <c r="F7" s="181"/>
+      <c r="G7" s="182">
         <v>40</v>
       </c>
-      <c r="H7" s="146">
+      <c r="H7" s="180">
         <v>40</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="148">
+      <c r="I7" s="183"/>
+      <c r="J7" s="182">
         <v>40</v>
       </c>
-      <c r="K7" s="146">
+      <c r="K7" s="180">
         <v>40</v>
       </c>
-      <c r="L7" s="147">
+      <c r="L7" s="181">
         <v>40</v>
       </c>
       <c r="M7" s="48">
@@ -2708,26 +2751,26 @@
       <c r="B8" s="47">
         <v>4</v>
       </c>
-      <c r="C8" s="144" t="s">
+      <c r="C8" s="178" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="145"/>
-      <c r="E8" s="146"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="148">
+      <c r="D8" s="179"/>
+      <c r="E8" s="180"/>
+      <c r="F8" s="181"/>
+      <c r="G8" s="182">
         <v>40</v>
       </c>
-      <c r="H8" s="146">
+      <c r="H8" s="180">
         <v>40</v>
       </c>
-      <c r="I8" s="56"/>
-      <c r="J8" s="148">
+      <c r="I8" s="183"/>
+      <c r="J8" s="182">
         <v>40</v>
       </c>
-      <c r="K8" s="146">
+      <c r="K8" s="180">
         <v>40</v>
       </c>
-      <c r="L8" s="147">
+      <c r="L8" s="181">
         <v>40</v>
       </c>
       <c r="M8" s="48">
@@ -2790,26 +2833,26 @@
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="144" t="s">
+      <c r="C9" s="178" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="145"/>
-      <c r="E9" s="146"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="148">
+      <c r="D9" s="179"/>
+      <c r="E9" s="180"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="182">
         <v>40</v>
       </c>
-      <c r="H9" s="146">
+      <c r="H9" s="180">
         <v>40</v>
       </c>
-      <c r="I9" s="56"/>
-      <c r="J9" s="148">
+      <c r="I9" s="183"/>
+      <c r="J9" s="182">
         <v>40</v>
       </c>
-      <c r="K9" s="146">
+      <c r="K9" s="180">
         <v>40</v>
       </c>
-      <c r="L9" s="147">
+      <c r="L9" s="181">
         <v>40</v>
       </c>
       <c r="M9" s="48">
@@ -2872,26 +2915,26 @@
       <c r="B10" s="47">
         <v>6</v>
       </c>
-      <c r="C10" s="144" t="s">
+      <c r="C10" s="178" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="145"/>
-      <c r="E10" s="146"/>
-      <c r="F10" s="147"/>
-      <c r="G10" s="148">
+      <c r="D10" s="179"/>
+      <c r="E10" s="180"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="182">
         <v>40</v>
       </c>
-      <c r="H10" s="146">
+      <c r="H10" s="180">
         <v>40</v>
       </c>
-      <c r="I10" s="56"/>
-      <c r="J10" s="148">
+      <c r="I10" s="183"/>
+      <c r="J10" s="182">
         <v>40</v>
       </c>
-      <c r="K10" s="146">
+      <c r="K10" s="180">
         <v>40</v>
       </c>
-      <c r="L10" s="147">
+      <c r="L10" s="181">
         <v>40</v>
       </c>
       <c r="M10" s="48">
@@ -2954,26 +2997,26 @@
       <c r="B11" s="47">
         <v>7</v>
       </c>
-      <c r="C11" s="144" t="s">
+      <c r="C11" s="178" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="145"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="148">
+      <c r="D11" s="179"/>
+      <c r="E11" s="180"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="182">
         <v>40</v>
       </c>
-      <c r="H11" s="146">
+      <c r="H11" s="180">
         <v>40</v>
       </c>
-      <c r="I11" s="56"/>
-      <c r="J11" s="148">
+      <c r="I11" s="183"/>
+      <c r="J11" s="182">
         <v>40</v>
       </c>
-      <c r="K11" s="146">
+      <c r="K11" s="180">
         <v>40</v>
       </c>
-      <c r="L11" s="147">
+      <c r="L11" s="181">
         <v>40</v>
       </c>
       <c r="M11" s="48">
@@ -3036,26 +3079,26 @@
       <c r="B12" s="47">
         <v>8</v>
       </c>
-      <c r="C12" s="144" t="s">
+      <c r="C12" s="178" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="145"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="148">
+      <c r="D12" s="179"/>
+      <c r="E12" s="180"/>
+      <c r="F12" s="181"/>
+      <c r="G12" s="182">
         <v>40</v>
       </c>
-      <c r="H12" s="146">
+      <c r="H12" s="180">
         <v>40</v>
       </c>
-      <c r="I12" s="56"/>
-      <c r="J12" s="148">
+      <c r="I12" s="183"/>
+      <c r="J12" s="182">
         <v>40</v>
       </c>
-      <c r="K12" s="146">
+      <c r="K12" s="180">
         <v>40</v>
       </c>
-      <c r="L12" s="147">
+      <c r="L12" s="181">
         <v>40</v>
       </c>
       <c r="M12" s="48">
@@ -3118,26 +3161,26 @@
       <c r="B13" s="47">
         <v>9</v>
       </c>
-      <c r="C13" s="144" t="s">
+      <c r="C13" s="178" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="145"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="148">
+      <c r="D13" s="179"/>
+      <c r="E13" s="180"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="182">
         <v>40</v>
       </c>
-      <c r="H13" s="146">
+      <c r="H13" s="180">
         <v>40</v>
       </c>
-      <c r="I13" s="56"/>
-      <c r="J13" s="148">
+      <c r="I13" s="183"/>
+      <c r="J13" s="182">
         <v>40</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="180">
         <v>40</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="181">
         <v>40</v>
       </c>
       <c r="M13" s="48">
@@ -3200,26 +3243,26 @@
       <c r="B14" s="47">
         <v>10</v>
       </c>
-      <c r="C14" s="144" t="s">
+      <c r="C14" s="178" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="145"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="147"/>
-      <c r="G14" s="148">
+      <c r="D14" s="179"/>
+      <c r="E14" s="180"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="182">
         <v>40</v>
       </c>
-      <c r="H14" s="146">
+      <c r="H14" s="180">
         <v>40</v>
       </c>
-      <c r="I14" s="56"/>
-      <c r="J14" s="148">
+      <c r="I14" s="183"/>
+      <c r="J14" s="182">
         <v>40</v>
       </c>
-      <c r="K14" s="146">
+      <c r="K14" s="180">
         <v>40</v>
       </c>
-      <c r="L14" s="147">
+      <c r="L14" s="181">
         <v>40</v>
       </c>
       <c r="M14" s="48">
@@ -3282,26 +3325,26 @@
       <c r="B15" s="47">
         <v>11</v>
       </c>
-      <c r="C15" s="144" t="s">
+      <c r="C15" s="178" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="145"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="147"/>
-      <c r="G15" s="148">
+      <c r="D15" s="179"/>
+      <c r="E15" s="180"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="182">
         <v>40</v>
       </c>
-      <c r="H15" s="146">
+      <c r="H15" s="180">
         <v>40</v>
       </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="148">
+      <c r="I15" s="183"/>
+      <c r="J15" s="182">
         <v>40</v>
       </c>
-      <c r="K15" s="146">
+      <c r="K15" s="180">
         <v>40</v>
       </c>
-      <c r="L15" s="147">
+      <c r="L15" s="181">
         <v>40</v>
       </c>
       <c r="M15" s="48">
@@ -3364,26 +3407,26 @@
       <c r="B16" s="47">
         <v>12</v>
       </c>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="178" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="145"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="147"/>
-      <c r="G16" s="148">
+      <c r="D16" s="179"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="182">
         <v>40</v>
       </c>
-      <c r="H16" s="146">
+      <c r="H16" s="180">
         <v>40</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="148">
+      <c r="I16" s="183"/>
+      <c r="J16" s="182">
         <v>40</v>
       </c>
-      <c r="K16" s="146">
+      <c r="K16" s="180">
         <v>40</v>
       </c>
-      <c r="L16" s="147">
+      <c r="L16" s="181">
         <v>40</v>
       </c>
       <c r="M16" s="48">
@@ -3446,26 +3489,26 @@
       <c r="B17" s="47">
         <v>13</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="178" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="145"/>
-      <c r="E17" s="146"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="148">
+      <c r="D17" s="179"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="181"/>
+      <c r="G17" s="182">
         <v>40</v>
       </c>
-      <c r="H17" s="146">
+      <c r="H17" s="180">
         <v>40</v>
       </c>
-      <c r="I17" s="56"/>
-      <c r="J17" s="148">
+      <c r="I17" s="183"/>
+      <c r="J17" s="182">
         <v>40</v>
       </c>
-      <c r="K17" s="146">
+      <c r="K17" s="180">
         <v>40</v>
       </c>
-      <c r="L17" s="147">
+      <c r="L17" s="181">
         <v>40</v>
       </c>
       <c r="M17" s="48">
@@ -3522,23 +3565,37 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="78"/>
+      <c r="A18" s="78">
+        <v>46205</v>
+      </c>
       <c r="B18" s="47">
         <v>14</v>
       </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="76"/>
+      <c r="C18" s="184" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="185"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="188">
+        <v>120</v>
+      </c>
+      <c r="H18" s="186">
+        <v>80</v>
+      </c>
+      <c r="I18" s="189"/>
+      <c r="J18" s="188">
+        <v>40</v>
+      </c>
+      <c r="K18" s="186">
+        <v>40</v>
+      </c>
+      <c r="L18" s="187">
+        <v>120</v>
+      </c>
       <c r="M18" s="48">
         <f t="shared" ref="M18:M20" si="29">SUM(D18:L18)/40</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N18" s="39">
         <f t="shared" si="18"/>
@@ -3550,11 +3607,11 @@
       </c>
       <c r="P18" s="73">
         <f t="shared" ref="P18:P20" si="30">SUM(G18:I18)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q18" s="40">
         <f t="shared" ref="Q18:Q20" si="31">SUM(J18:L18)/20</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R18" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3590,23 +3647,33 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="78"/>
+      <c r="A19" s="78">
+        <v>46205</v>
+      </c>
       <c r="B19" s="47">
         <v>15</v>
       </c>
-      <c r="C19" s="57"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="76"/>
+      <c r="C19" s="184" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="185"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="187"/>
+      <c r="G19" s="188"/>
+      <c r="H19" s="186"/>
+      <c r="I19" s="189"/>
+      <c r="J19" s="188">
+        <v>120</v>
+      </c>
+      <c r="K19" s="186">
+        <v>120</v>
+      </c>
+      <c r="L19" s="187">
+        <v>120</v>
+      </c>
       <c r="M19" s="48">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N19" s="39">
         <f t="shared" si="18"/>
@@ -3622,7 +3689,7 @@
       </c>
       <c r="Q19" s="40">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R19" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3658,23 +3725,33 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="78"/>
+      <c r="A20" s="78">
+        <v>46205</v>
+      </c>
       <c r="B20" s="47">
         <v>16</v>
       </c>
-      <c r="C20" s="57"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="76"/>
+      <c r="C20" s="184" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="185"/>
+      <c r="E20" s="186"/>
+      <c r="F20" s="187"/>
+      <c r="G20" s="188"/>
+      <c r="H20" s="186"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="188">
+        <v>240</v>
+      </c>
+      <c r="K20" s="186">
+        <v>240</v>
+      </c>
+      <c r="L20" s="187">
+        <v>240</v>
+      </c>
       <c r="M20" s="48">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N20" s="39">
         <f t="shared" si="18"/>
@@ -3690,7 +3767,7 @@
       </c>
       <c r="Q20" s="40">
         <f t="shared" si="31"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="R20" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3726,23 +3803,37 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="78"/>
+      <c r="A21" s="78">
+        <v>46205</v>
+      </c>
       <c r="B21" s="47">
         <v>17</v>
       </c>
-      <c r="C21" s="57"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="50"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="76"/>
+      <c r="C21" s="184" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="185"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="187"/>
+      <c r="G21" s="188">
+        <v>40</v>
+      </c>
+      <c r="H21" s="186">
+        <v>40</v>
+      </c>
+      <c r="I21" s="189"/>
+      <c r="J21" s="188">
+        <v>40</v>
+      </c>
+      <c r="K21" s="186">
+        <v>40</v>
+      </c>
+      <c r="L21" s="187">
+        <v>40</v>
+      </c>
       <c r="M21" s="48">
         <f t="shared" ref="M21:M23" si="37">SUM(D21:L21)/40</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N21" s="39">
         <f t="shared" si="18"/>
@@ -3754,11 +3845,11 @@
       </c>
       <c r="P21" s="73">
         <f t="shared" ref="P21:P23" si="38">SUM(G21:I21)/20</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q21" s="40">
         <f t="shared" ref="Q21:Q23" si="39">SUM(J21:L21)/20</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R21" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11007,10 +11098,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="159" t="s">
+      <c r="B132" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="160"/>
+      <c r="C132" s="163"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11025,11 +11116,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>520</v>
+        <v>680</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>520</v>
+        <v>640</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11037,19 +11128,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>520</v>
+        <v>960</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>520</v>
+        <v>960</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>520</v>
+        <v>1040</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11061,11 +11152,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11274,10 +11365,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="172" t="s">
+      <c r="B136" s="150" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="173"/>
+      <c r="C136" s="151"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11368,10 +11459,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="161" t="s">
+      <c r="B137" s="139" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="162"/>
+      <c r="C137" s="140"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11386,11 +11477,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>520</v>
+        <v>680</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>520</v>
+        <v>640</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11398,19 +11489,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>520</v>
+        <v>960</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>520</v>
+        <v>960</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>520</v>
+        <v>1040</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11422,11 +11513,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11463,17 +11554,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11503,24 +11594,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="174" t="s">
+      <c r="C3" s="164" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="178" t="s">
+      <c r="D3" s="165"/>
+      <c r="E3" s="165"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="168" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="179"/>
-      <c r="K3" s="180" t="s">
+      <c r="I3" s="169"/>
+      <c r="K3" s="170" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="180"/>
-      <c r="M3" s="180"/>
-      <c r="N3" s="180"/>
-      <c r="O3" s="180"/>
+      <c r="L3" s="170"/>
+      <c r="M3" s="170"/>
+      <c r="N3" s="170"/>
+      <c r="O3" s="170"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -11704,14 +11795,14 @@
       <c r="O10" s="81"/>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="177" t="s">
+      <c r="C11" s="167" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="177"/>
-      <c r="F11" s="177" t="s">
+      <c r="D11" s="167"/>
+      <c r="F11" s="167" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="177"/>
+      <c r="G11" s="167"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -12017,20 +12108,23 @@
       <c r="K2" s="81" t="s">
         <v>100</v>
       </c>
+      <c r="L2" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="I3" s="81" t="s">
+      <c r="I3" s="171" t="s">
         <v>101</v>
       </c>
-      <c r="J3" s="81">
+      <c r="J3" s="171">
         <v>10</v>
       </c>
-      <c r="K3" s="81" t="s">
-        <v>105</v>
+      <c r="K3" s="171" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -12038,14 +12132,14 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="I4" s="81" t="s">
+      <c r="I4" s="171" t="s">
         <v>102</v>
       </c>
-      <c r="J4" s="81">
+      <c r="J4" s="171">
         <v>9</v>
       </c>
-      <c r="K4" s="81" t="s">
-        <v>105</v>
+      <c r="K4" s="171" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -12053,14 +12147,14 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="I5" s="81" t="s">
+      <c r="I5" s="171" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="81">
+      <c r="J5" s="171">
         <v>18</v>
       </c>
-      <c r="K5" s="81" t="s">
-        <v>105</v>
+      <c r="K5" s="171" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -12068,14 +12162,14 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="171" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="81">
+      <c r="J6" s="171">
         <v>5</v>
       </c>
-      <c r="K6" s="81" t="s">
-        <v>105</v>
+      <c r="K6" s="171" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -12083,9 +12177,15 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
+      <c r="I7" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" s="81">
+        <v>14</v>
+      </c>
+      <c r="K7" s="81" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
@@ -12095,9 +12195,15 @@
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
       <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
+      <c r="I8" s="81" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="81">
+        <v>13</v>
+      </c>
+      <c r="K8" s="81" t="s">
+        <v>110</v>
+      </c>
       <c r="L8" s="133"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -12105,9 +12211,15 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
+      <c r="I9" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="J9" s="81">
+        <v>4</v>
+      </c>
+      <c r="K9" s="81" t="s">
+        <v>110</v>
+      </c>
       <c r="L9" s="133"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -12115,9 +12227,15 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="81"/>
-      <c r="K10" s="81"/>
+      <c r="I10" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="J10" s="81">
+        <v>12</v>
+      </c>
+      <c r="K10" s="81" t="s">
+        <v>110</v>
+      </c>
       <c r="L10" s="133"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -12125,9 +12243,15 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
+      <c r="I11" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="81">
+        <v>19</v>
+      </c>
+      <c r="K11" s="81" t="s">
+        <v>110</v>
+      </c>
       <c r="L11" s="133"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5457CF98-FD11-44C8-A765-8B9375118901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C5D86-8B46-482F-8CEB-95D29A98C7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="115">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -366,6 +366,9 @@
   <si>
     <t xml:space="preserve">Umaima  paragon City </t>
   </si>
+  <si>
+    <t xml:space="preserve">Rainbow Model Town </t>
+  </si>
 </sst>
 </file>
 
@@ -1259,7 +1262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1619,125 +1622,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1747,6 +1641,105 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2312,7 +2305,7 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="149" t="s">
+      <c r="A2" s="174" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="153" t="s">
@@ -2348,13 +2341,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="141"/>
-      <c r="N2" s="142"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="144" t="s">
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="145"/>
+      <c r="Q2" s="170"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2373,7 +2366,7 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="149"/>
+      <c r="A3" s="174"/>
       <c r="B3" s="154"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
@@ -2405,11 +2398,11 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="146" t="s">
+      <c r="M3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="147"/>
-      <c r="O3" s="148"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
       <c r="R3" s="156" t="s">
@@ -2426,7 +2419,7 @@
       <c r="Y3" s="161"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="149"/>
+      <c r="A4" s="174"/>
       <c r="B4" s="155"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
@@ -2505,26 +2498,26 @@
       <c r="B5" s="36">
         <v>1</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="173"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="176">
+      <c r="D5" s="141"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="143">
         <v>40</v>
       </c>
-      <c r="H5" s="174">
+      <c r="H5" s="142">
         <v>40</v>
       </c>
-      <c r="I5" s="175"/>
-      <c r="J5" s="176">
+      <c r="I5" s="38"/>
+      <c r="J5" s="143">
         <v>40</v>
       </c>
-      <c r="K5" s="174">
+      <c r="K5" s="142">
         <v>40</v>
       </c>
-      <c r="L5" s="177">
+      <c r="L5" s="144">
         <v>40</v>
       </c>
       <c r="M5" s="37">
@@ -2587,26 +2580,26 @@
       <c r="B6" s="47">
         <v>2</v>
       </c>
-      <c r="C6" s="178" t="s">
+      <c r="C6" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="179"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="181"/>
-      <c r="G6" s="182">
+      <c r="D6" s="74"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="50">
         <v>80</v>
       </c>
-      <c r="H6" s="180">
+      <c r="H6" s="75">
         <v>80</v>
       </c>
-      <c r="I6" s="183"/>
-      <c r="J6" s="182">
+      <c r="I6" s="49"/>
+      <c r="J6" s="50">
         <v>80</v>
       </c>
-      <c r="K6" s="180">
+      <c r="K6" s="75">
         <v>80</v>
       </c>
-      <c r="L6" s="181">
+      <c r="L6" s="76">
         <v>80</v>
       </c>
       <c r="M6" s="48">
@@ -2669,26 +2662,26 @@
       <c r="B7" s="47">
         <v>3</v>
       </c>
-      <c r="C7" s="178" t="s">
+      <c r="C7" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="179"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="182">
+      <c r="D7" s="74"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="50">
         <v>40</v>
       </c>
-      <c r="H7" s="180">
+      <c r="H7" s="75">
         <v>40</v>
       </c>
-      <c r="I7" s="183"/>
-      <c r="J7" s="182">
+      <c r="I7" s="49"/>
+      <c r="J7" s="50">
         <v>40</v>
       </c>
-      <c r="K7" s="180">
+      <c r="K7" s="75">
         <v>40</v>
       </c>
-      <c r="L7" s="181">
+      <c r="L7" s="76">
         <v>40</v>
       </c>
       <c r="M7" s="48">
@@ -2751,26 +2744,26 @@
       <c r="B8" s="47">
         <v>4</v>
       </c>
-      <c r="C8" s="178" t="s">
+      <c r="C8" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="179"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="181"/>
-      <c r="G8" s="182">
+      <c r="D8" s="74"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="50">
         <v>40</v>
       </c>
-      <c r="H8" s="180">
+      <c r="H8" s="75">
         <v>40</v>
       </c>
-      <c r="I8" s="183"/>
-      <c r="J8" s="182">
+      <c r="I8" s="49"/>
+      <c r="J8" s="50">
         <v>40</v>
       </c>
-      <c r="K8" s="180">
+      <c r="K8" s="75">
         <v>40</v>
       </c>
-      <c r="L8" s="181">
+      <c r="L8" s="76">
         <v>40</v>
       </c>
       <c r="M8" s="48">
@@ -2833,26 +2826,26 @@
       <c r="B9" s="47">
         <v>5</v>
       </c>
-      <c r="C9" s="178" t="s">
+      <c r="C9" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="179"/>
-      <c r="E9" s="180"/>
-      <c r="F9" s="181"/>
-      <c r="G9" s="182">
+      <c r="D9" s="74"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="50">
         <v>40</v>
       </c>
-      <c r="H9" s="180">
+      <c r="H9" s="75">
         <v>40</v>
       </c>
-      <c r="I9" s="183"/>
-      <c r="J9" s="182">
+      <c r="I9" s="49"/>
+      <c r="J9" s="50">
         <v>40</v>
       </c>
-      <c r="K9" s="180">
+      <c r="K9" s="75">
         <v>40</v>
       </c>
-      <c r="L9" s="181">
+      <c r="L9" s="76">
         <v>40</v>
       </c>
       <c r="M9" s="48">
@@ -2915,26 +2908,26 @@
       <c r="B10" s="47">
         <v>6</v>
       </c>
-      <c r="C10" s="178" t="s">
+      <c r="C10" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="179"/>
-      <c r="E10" s="180"/>
-      <c r="F10" s="181"/>
-      <c r="G10" s="182">
+      <c r="D10" s="74"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="50">
         <v>40</v>
       </c>
-      <c r="H10" s="180">
+      <c r="H10" s="75">
         <v>40</v>
       </c>
-      <c r="I10" s="183"/>
-      <c r="J10" s="182">
+      <c r="I10" s="49"/>
+      <c r="J10" s="50">
         <v>40</v>
       </c>
-      <c r="K10" s="180">
+      <c r="K10" s="75">
         <v>40</v>
       </c>
-      <c r="L10" s="181">
+      <c r="L10" s="76">
         <v>40</v>
       </c>
       <c r="M10" s="48">
@@ -2997,26 +2990,26 @@
       <c r="B11" s="47">
         <v>7</v>
       </c>
-      <c r="C11" s="178" t="s">
+      <c r="C11" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="181"/>
-      <c r="G11" s="182">
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="50">
         <v>40</v>
       </c>
-      <c r="H11" s="180">
+      <c r="H11" s="75">
         <v>40</v>
       </c>
-      <c r="I11" s="183"/>
-      <c r="J11" s="182">
+      <c r="I11" s="49"/>
+      <c r="J11" s="50">
         <v>40</v>
       </c>
-      <c r="K11" s="180">
+      <c r="K11" s="75">
         <v>40</v>
       </c>
-      <c r="L11" s="181">
+      <c r="L11" s="76">
         <v>40</v>
       </c>
       <c r="M11" s="48">
@@ -3079,26 +3072,26 @@
       <c r="B12" s="47">
         <v>8</v>
       </c>
-      <c r="C12" s="178" t="s">
+      <c r="C12" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="179"/>
-      <c r="E12" s="180"/>
-      <c r="F12" s="181"/>
-      <c r="G12" s="182">
+      <c r="D12" s="74"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="50">
         <v>40</v>
       </c>
-      <c r="H12" s="180">
+      <c r="H12" s="75">
         <v>40</v>
       </c>
-      <c r="I12" s="183"/>
-      <c r="J12" s="182">
+      <c r="I12" s="49"/>
+      <c r="J12" s="50">
         <v>40</v>
       </c>
-      <c r="K12" s="180">
+      <c r="K12" s="75">
         <v>40</v>
       </c>
-      <c r="L12" s="181">
+      <c r="L12" s="76">
         <v>40</v>
       </c>
       <c r="M12" s="48">
@@ -3161,26 +3154,26 @@
       <c r="B13" s="47">
         <v>9</v>
       </c>
-      <c r="C13" s="178" t="s">
+      <c r="C13" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="179"/>
-      <c r="E13" s="180"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="182">
+      <c r="D13" s="74"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="50">
         <v>40</v>
       </c>
-      <c r="H13" s="180">
+      <c r="H13" s="75">
         <v>40</v>
       </c>
-      <c r="I13" s="183"/>
-      <c r="J13" s="182">
+      <c r="I13" s="49"/>
+      <c r="J13" s="50">
         <v>40</v>
       </c>
-      <c r="K13" s="180">
+      <c r="K13" s="75">
         <v>40</v>
       </c>
-      <c r="L13" s="181">
+      <c r="L13" s="76">
         <v>40</v>
       </c>
       <c r="M13" s="48">
@@ -3243,26 +3236,26 @@
       <c r="B14" s="47">
         <v>10</v>
       </c>
-      <c r="C14" s="178" t="s">
+      <c r="C14" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="179"/>
-      <c r="E14" s="180"/>
-      <c r="F14" s="181"/>
-      <c r="G14" s="182">
+      <c r="D14" s="74"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="50">
         <v>40</v>
       </c>
-      <c r="H14" s="180">
+      <c r="H14" s="75">
         <v>40</v>
       </c>
-      <c r="I14" s="183"/>
-      <c r="J14" s="182">
+      <c r="I14" s="49"/>
+      <c r="J14" s="50">
         <v>40</v>
       </c>
-      <c r="K14" s="180">
+      <c r="K14" s="75">
         <v>40</v>
       </c>
-      <c r="L14" s="181">
+      <c r="L14" s="76">
         <v>40</v>
       </c>
       <c r="M14" s="48">
@@ -3325,26 +3318,26 @@
       <c r="B15" s="47">
         <v>11</v>
       </c>
-      <c r="C15" s="178" t="s">
+      <c r="C15" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="179"/>
-      <c r="E15" s="180"/>
-      <c r="F15" s="181"/>
-      <c r="G15" s="182">
+      <c r="D15" s="74"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="50">
         <v>40</v>
       </c>
-      <c r="H15" s="180">
+      <c r="H15" s="75">
         <v>40</v>
       </c>
-      <c r="I15" s="183"/>
-      <c r="J15" s="182">
+      <c r="I15" s="49"/>
+      <c r="J15" s="50">
         <v>40</v>
       </c>
-      <c r="K15" s="180">
+      <c r="K15" s="75">
         <v>40</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="76">
         <v>40</v>
       </c>
       <c r="M15" s="48">
@@ -3407,26 +3400,26 @@
       <c r="B16" s="47">
         <v>12</v>
       </c>
-      <c r="C16" s="178" t="s">
+      <c r="C16" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="179"/>
-      <c r="E16" s="180"/>
-      <c r="F16" s="181"/>
-      <c r="G16" s="182">
+      <c r="D16" s="74"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="50">
         <v>40</v>
       </c>
-      <c r="H16" s="180">
+      <c r="H16" s="75">
         <v>40</v>
       </c>
-      <c r="I16" s="183"/>
-      <c r="J16" s="182">
+      <c r="I16" s="49"/>
+      <c r="J16" s="50">
         <v>40</v>
       </c>
-      <c r="K16" s="180">
+      <c r="K16" s="75">
         <v>40</v>
       </c>
-      <c r="L16" s="181">
+      <c r="L16" s="76">
         <v>40</v>
       </c>
       <c r="M16" s="48">
@@ -3489,26 +3482,26 @@
       <c r="B17" s="47">
         <v>13</v>
       </c>
-      <c r="C17" s="178" t="s">
+      <c r="C17" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="179"/>
-      <c r="E17" s="180"/>
-      <c r="F17" s="181"/>
-      <c r="G17" s="182">
+      <c r="D17" s="74"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="50">
         <v>40</v>
       </c>
-      <c r="H17" s="180">
+      <c r="H17" s="75">
         <v>40</v>
       </c>
-      <c r="I17" s="183"/>
-      <c r="J17" s="182">
+      <c r="I17" s="49"/>
+      <c r="J17" s="50">
         <v>40</v>
       </c>
-      <c r="K17" s="180">
+      <c r="K17" s="75">
         <v>40</v>
       </c>
-      <c r="L17" s="181">
+      <c r="L17" s="76">
         <v>40</v>
       </c>
       <c r="M17" s="48">
@@ -3571,26 +3564,26 @@
       <c r="B18" s="47">
         <v>14</v>
       </c>
-      <c r="C18" s="184" t="s">
+      <c r="C18" s="145" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="185"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="187"/>
-      <c r="G18" s="188">
+      <c r="D18" s="146"/>
+      <c r="E18" s="147"/>
+      <c r="F18" s="148"/>
+      <c r="G18" s="149">
         <v>120</v>
       </c>
-      <c r="H18" s="186">
+      <c r="H18" s="147">
         <v>80</v>
       </c>
-      <c r="I18" s="189"/>
-      <c r="J18" s="188">
+      <c r="I18" s="150"/>
+      <c r="J18" s="149">
         <v>40</v>
       </c>
-      <c r="K18" s="186">
+      <c r="K18" s="147">
         <v>40</v>
       </c>
-      <c r="L18" s="187">
+      <c r="L18" s="148">
         <v>120</v>
       </c>
       <c r="M18" s="48">
@@ -3653,22 +3646,22 @@
       <c r="B19" s="47">
         <v>15</v>
       </c>
-      <c r="C19" s="184" t="s">
+      <c r="C19" s="145" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="185"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="187"/>
-      <c r="G19" s="188"/>
-      <c r="H19" s="186"/>
-      <c r="I19" s="189"/>
-      <c r="J19" s="188">
+      <c r="D19" s="146"/>
+      <c r="E19" s="147"/>
+      <c r="F19" s="148"/>
+      <c r="G19" s="149"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="150"/>
+      <c r="J19" s="149">
         <v>120</v>
       </c>
-      <c r="K19" s="186">
+      <c r="K19" s="147">
         <v>120</v>
       </c>
-      <c r="L19" s="187">
+      <c r="L19" s="148">
         <v>120</v>
       </c>
       <c r="M19" s="48">
@@ -3731,22 +3724,22 @@
       <c r="B20" s="47">
         <v>16</v>
       </c>
-      <c r="C20" s="184" t="s">
+      <c r="C20" s="145" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="185"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="187"/>
-      <c r="G20" s="188"/>
-      <c r="H20" s="186"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="188">
+      <c r="D20" s="146"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="148"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="147"/>
+      <c r="I20" s="150"/>
+      <c r="J20" s="149">
         <v>240</v>
       </c>
-      <c r="K20" s="186">
+      <c r="K20" s="147">
         <v>240</v>
       </c>
-      <c r="L20" s="187">
+      <c r="L20" s="148">
         <v>240</v>
       </c>
       <c r="M20" s="48">
@@ -3809,26 +3802,26 @@
       <c r="B21" s="47">
         <v>17</v>
       </c>
-      <c r="C21" s="184" t="s">
+      <c r="C21" s="145" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="185"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="187"/>
-      <c r="G21" s="188">
+      <c r="D21" s="146"/>
+      <c r="E21" s="147"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="149">
         <v>40</v>
       </c>
-      <c r="H21" s="186">
+      <c r="H21" s="147">
         <v>40</v>
       </c>
-      <c r="I21" s="189"/>
-      <c r="J21" s="188">
+      <c r="I21" s="150"/>
+      <c r="J21" s="149">
         <v>40</v>
       </c>
-      <c r="K21" s="186">
+      <c r="K21" s="147">
         <v>40</v>
       </c>
-      <c r="L21" s="187">
+      <c r="L21" s="148">
         <v>40</v>
       </c>
       <c r="M21" s="48">
@@ -3889,19 +3882,31 @@
       <c r="B22" s="47">
         <v>18</v>
       </c>
-      <c r="C22" s="57"/>
+      <c r="C22" s="57" t="s">
+        <v>107</v>
+      </c>
       <c r="D22" s="74"/>
       <c r="E22" s="75"/>
       <c r="F22" s="76"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="75"/>
+      <c r="G22" s="50">
+        <v>78</v>
+      </c>
+      <c r="H22" s="75">
+        <v>77</v>
+      </c>
       <c r="I22" s="49"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="76"/>
+      <c r="J22" s="50">
+        <v>159</v>
+      </c>
+      <c r="K22" s="75">
+        <v>38</v>
+      </c>
+      <c r="L22" s="76">
+        <v>158</v>
+      </c>
       <c r="M22" s="48">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="N22" s="39">
         <f t="shared" si="18"/>
@@ -3913,11 +3918,11 @@
       </c>
       <c r="P22" s="73">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q22" s="40">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="R22" s="51" t="e">
         <f t="shared" si="4"/>
@@ -3957,19 +3962,29 @@
       <c r="B23" s="47">
         <v>19</v>
       </c>
-      <c r="C23" s="57"/>
+      <c r="C23" s="57" t="s">
+        <v>114</v>
+      </c>
       <c r="D23" s="74"/>
       <c r="E23" s="75"/>
       <c r="F23" s="76"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="75"/>
+      <c r="H23" s="75">
+        <v>40</v>
+      </c>
       <c r="I23" s="49"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="76"/>
+      <c r="J23" s="50">
+        <v>40</v>
+      </c>
+      <c r="K23" s="75">
+        <v>40</v>
+      </c>
+      <c r="L23" s="76">
+        <v>40</v>
+      </c>
       <c r="M23" s="48">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" s="39">
         <f t="shared" si="18"/>
@@ -3981,11 +3996,11 @@
       </c>
       <c r="P23" s="73">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="40">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R23" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4025,19 +4040,31 @@
       <c r="B24" s="47">
         <v>20</v>
       </c>
-      <c r="C24" s="57"/>
+      <c r="C24" s="57" t="s">
+        <v>106</v>
+      </c>
       <c r="D24" s="74"/>
       <c r="E24" s="75"/>
       <c r="F24" s="76"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="75"/>
+      <c r="G24" s="50">
+        <v>120</v>
+      </c>
+      <c r="H24" s="75">
+        <v>120</v>
+      </c>
       <c r="I24" s="49"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
+      <c r="J24" s="50">
+        <v>160</v>
+      </c>
+      <c r="K24" s="75">
+        <v>0</v>
+      </c>
+      <c r="L24" s="76">
+        <v>160</v>
+      </c>
       <c r="M24" s="48">
         <f t="shared" ref="M24:M27" si="47">SUM(D24:L24)/40</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N24" s="39">
         <f t="shared" si="18"/>
@@ -4049,11 +4076,11 @@
       </c>
       <c r="P24" s="73">
         <f t="shared" ref="P24:P27" si="48">SUM(G24:I24)/20</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q24" s="40">
         <f t="shared" ref="Q24:Q27" si="49">SUM(J24:L24)/20</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R24" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11116,11 +11143,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>680</v>
+        <v>878</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>640</v>
+        <v>877</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11128,19 +11155,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>960</v>
+        <v>1319</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>960</v>
+        <v>1038</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>1040</v>
+        <v>1398</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>107</v>
+        <v>137.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11152,11 +11179,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>66</v>
+        <v>87.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>148</v>
+        <v>187.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11365,10 +11392,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="150" t="s">
+      <c r="B136" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="151"/>
+      <c r="C136" s="176"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11459,10 +11486,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="139" t="s">
+      <c r="B137" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="140"/>
+      <c r="C137" s="165"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11477,11 +11504,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>680</v>
+        <v>878</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>640</v>
+        <v>877</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11489,19 +11516,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>960</v>
+        <v>1319</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>960</v>
+        <v>1038</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>1040</v>
+        <v>1398</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>107</v>
+        <v>137.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11513,11 +11540,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>136</v>
+        <v>179.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>302</v>
+        <v>381.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11554,17 +11581,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11594,24 +11621,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="164" t="s">
+      <c r="C3" s="177" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="165"/>
-      <c r="E3" s="165"/>
-      <c r="F3" s="165"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="168" t="s">
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="179"/>
+      <c r="H3" s="181" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="169"/>
-      <c r="K3" s="170" t="s">
+      <c r="I3" s="182"/>
+      <c r="K3" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="170"/>
-      <c r="M3" s="170"/>
-      <c r="N3" s="170"/>
-      <c r="O3" s="170"/>
+      <c r="L3" s="183"/>
+      <c r="M3" s="183"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="183"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -11654,20 +11681,20 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>35.85</v>
+        <v>108</v>
       </c>
       <c r="E5" s="79">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="F5" s="79"/>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>105.85</v>
+        <v>251</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>105.85</v>
+        <v>251</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11675,12 +11702,16 @@
       <c r="L5" s="7">
         <v>70</v>
       </c>
-      <c r="M5" s="5"/>
+      <c r="M5" s="5">
+        <v>9586</v>
+      </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="81"/>
+        <v>239.65</v>
+      </c>
+      <c r="O5" s="81">
+        <v>186</v>
+      </c>
     </row>
     <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C6" s="107" t="s">
@@ -11688,11 +11719,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>1434</v>
+        <v>4320</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>2800</v>
+        <v>5720</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -11700,7 +11731,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>4234</v>
+        <v>10040</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11708,7 +11739,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>4234</v>
+        <v>10040</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11716,12 +11747,16 @@
       <c r="L6" s="7">
         <v>70</v>
       </c>
-      <c r="M6" s="5"/>
+      <c r="M6" s="5">
+        <v>10668</v>
+      </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="81"/>
+        <v>266.7</v>
+      </c>
+      <c r="O6" s="81">
+        <v>103</v>
+      </c>
     </row>
     <row r="7" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C7" s="90"/>
@@ -11736,7 +11771,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O7" s="81"/>
+      <c r="O7" s="81">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C8" s="82" t="s">
@@ -11748,12 +11785,16 @@
       <c r="L8" s="7">
         <v>120</v>
       </c>
-      <c r="M8" s="5"/>
+      <c r="M8" s="5">
+        <v>10905</v>
+      </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="81"/>
+        <v>272.625</v>
+      </c>
+      <c r="O8" s="81">
+        <v>63</v>
+      </c>
     </row>
     <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C9" s="82" t="s">
@@ -11761,11 +11802,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-35.85</v>
+        <v>-108</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-70</v>
+        <v>-143</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -11773,12 +11814,16 @@
       <c r="L9" s="7">
         <v>120</v>
       </c>
-      <c r="M9" s="5"/>
+      <c r="M9" s="5">
+        <v>5595</v>
+      </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="81"/>
+        <v>139.875</v>
+      </c>
+      <c r="O9" s="81">
+        <v>130</v>
+      </c>
     </row>
     <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K10" s="1" t="s">
@@ -11787,34 +11832,42 @@
       <c r="L10" s="7">
         <v>120</v>
       </c>
-      <c r="M10" s="5"/>
+      <c r="M10" s="5">
+        <v>7110</v>
+      </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="81"/>
+        <v>177.75</v>
+      </c>
+      <c r="O10" s="81">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="180" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="167"/>
-      <c r="F11" s="167" t="s">
+      <c r="D11" s="180"/>
+      <c r="F11" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="167"/>
+      <c r="G11" s="180"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L11" s="7">
         <v>60</v>
       </c>
-      <c r="M11" s="5"/>
+      <c r="M11" s="5">
+        <v>66124</v>
+      </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="81"/>
+        <v>1653.1</v>
+      </c>
+      <c r="O11" s="81">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="93" t="s">
@@ -11828,7 +11881,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>3539.85</v>
+        <v>3685</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11836,15 +11889,15 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>0</v>
+        <v>109988</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>0</v>
+        <v>2749.7</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
-        <v>0</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
@@ -11860,7 +11913,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>141594</v>
+        <v>147400</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -11895,7 +11948,7 @@
       </c>
       <c r="O17" s="127">
         <f>N17-M5</f>
-        <v>13270</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="18" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11913,7 +11966,7 @@
       </c>
       <c r="O18" s="127">
         <f>N18-M6</f>
-        <v>14352</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="19" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11949,7 +12002,7 @@
       </c>
       <c r="O20" s="127">
         <f t="shared" si="1"/>
-        <v>12294</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="21" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11967,7 +12020,7 @@
       </c>
       <c r="O21" s="127">
         <f t="shared" si="1"/>
-        <v>6522</v>
+        <v>927</v>
       </c>
     </row>
     <row r="22" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11985,7 +12038,7 @@
       </c>
       <c r="O22" s="127">
         <f t="shared" si="1"/>
-        <v>9539</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="23" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -12003,7 +12056,7 @@
       </c>
       <c r="O23" s="127">
         <f t="shared" si="1"/>
-        <v>57991</v>
+        <v>-8133</v>
       </c>
     </row>
     <row r="24" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12021,7 +12074,7 @@
       </c>
       <c r="O24" s="122">
         <f>SUM(O17:O23)</f>
-        <v>114978</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="25" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12039,7 +12092,7 @@
       </c>
       <c r="O25" s="122">
         <f>O24/40</f>
-        <v>2874.45</v>
+        <v>124.75</v>
       </c>
     </row>
   </sheetData>
@@ -12117,13 +12170,13 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="I3" s="171" t="s">
+      <c r="I3" s="139" t="s">
         <v>101</v>
       </c>
-      <c r="J3" s="171">
+      <c r="J3" s="139">
         <v>10</v>
       </c>
-      <c r="K3" s="171" t="s">
+      <c r="K3" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12132,13 +12185,13 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="I4" s="171" t="s">
+      <c r="I4" s="139" t="s">
         <v>102</v>
       </c>
-      <c r="J4" s="171">
+      <c r="J4" s="139">
         <v>9</v>
       </c>
-      <c r="K4" s="171" t="s">
+      <c r="K4" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12147,13 +12200,13 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="I5" s="171" t="s">
+      <c r="I5" s="139" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="171">
+      <c r="J5" s="139">
         <v>18</v>
       </c>
-      <c r="K5" s="171" t="s">
+      <c r="K5" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12162,13 +12215,13 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="I6" s="171" t="s">
+      <c r="I6" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="171">
+      <c r="J6" s="139">
         <v>5</v>
       </c>
-      <c r="K6" s="171" t="s">
+      <c r="K6" s="139" t="s">
         <v>100</v>
       </c>
     </row>
@@ -12184,7 +12237,7 @@
         <v>14</v>
       </c>
       <c r="K7" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -12194,7 +12247,9 @@
       <c r="D8" s="2"/>
       <c r="F8" s="81"/>
       <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
+      <c r="H8" s="81" t="s">
+        <v>105</v>
+      </c>
       <c r="I8" s="81" t="s">
         <v>107</v>
       </c>
@@ -12202,7 +12257,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L8" s="133"/>
     </row>
@@ -12211,6 +12266,9 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
+      <c r="H9" t="s">
+        <v>105</v>
+      </c>
       <c r="I9" s="81" t="s">
         <v>108</v>
       </c>
@@ -12218,7 +12276,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="81" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L9" s="133"/>
     </row>
@@ -12227,13 +12285,13 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="I10" s="81" t="s">
+      <c r="I10" s="151" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="81">
+      <c r="J10" s="151">
         <v>12</v>
       </c>
-      <c r="K10" s="81" t="s">
+      <c r="K10" s="151" t="s">
         <v>110</v>
       </c>
       <c r="L10" s="133"/>
@@ -12243,13 +12301,13 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
-      <c r="I11" s="81" t="s">
+      <c r="I11" s="151" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="81">
+      <c r="J11" s="151">
         <v>19</v>
       </c>
-      <c r="K11" s="81" t="s">
+      <c r="K11" s="151" t="s">
         <v>110</v>
       </c>
       <c r="L11" s="133"/>

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C5D86-8B46-482F-8CEB-95D29A98C7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8E1D61-6FF3-4C2E-AF03-329D42A1A8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -369,6 +369,9 @@
   <si>
     <t xml:space="preserve">Rainbow Model Town </t>
   </si>
+  <si>
+    <t>Opening July 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -1645,6 +1648,45 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1681,44 +1723,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1736,9 +1742,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2276,14 +2279,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="152">
+      <c r="B1" s="165">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
-      </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
+        <v>46209</v>
+      </c>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2305,10 +2308,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="166" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2341,13 +2344,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="M2" s="154"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="170"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2366,8 +2369,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="174"/>
-      <c r="B3" s="154"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2398,29 +2401,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="156" t="s">
+      <c r="R3" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="157"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="159" t="s">
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="161"/>
+      <c r="W3" s="173"/>
+      <c r="X3" s="173"/>
+      <c r="Y3" s="174"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="174"/>
-      <c r="B4" s="155"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11125,10 +11128,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="162" t="s">
+      <c r="B132" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="163"/>
+      <c r="C132" s="176"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11392,10 +11395,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="175" t="s">
+      <c r="B136" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="176"/>
+      <c r="C136" s="164"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11486,10 +11489,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="164" t="s">
+      <c r="B137" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="165"/>
+      <c r="C137" s="153"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11581,17 +11584,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11602,7 +11605,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:O25"/>
+  <dimension ref="C2:P29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -11611,7 +11614,7 @@
     <col min="4" max="4" width="13.08984375" customWidth="1"/>
     <col min="5" max="6" width="12.36328125" customWidth="1"/>
     <col min="7" max="7" width="11.26953125" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="38.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.08984375" bestFit="1" customWidth="1"/>
@@ -11621,24 +11624,24 @@
   <sheetData>
     <row r="2" spans="3:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="3:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="179"/>
-      <c r="H3" s="181" t="s">
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="180"/>
+      <c r="H3" s="182" t="s">
         <v>65</v>
       </c>
-      <c r="I3" s="182"/>
-      <c r="K3" s="183" t="s">
+      <c r="I3" s="183"/>
+      <c r="K3" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="183"/>
-      <c r="M3" s="183"/>
-      <c r="N3" s="183"/>
-      <c r="O3" s="183"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
     </row>
     <row r="4" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="103"/>
@@ -11681,20 +11684,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="E5" s="79">
-        <v>143</v>
-      </c>
-      <c r="F5" s="79"/>
+        <v>183</v>
+      </c>
+      <c r="F5" s="79">
+        <v>300</v>
+      </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>251</v>
+        <v>669</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>251</v>
+        <v>669</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11703,14 +11708,14 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>9586</v>
+        <v>6804</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>239.65</v>
+        <v>170.1</v>
       </c>
       <c r="O5" s="81">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="3:15" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -11719,19 +11724,19 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>4320</v>
+        <v>7440</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>5720</v>
+        <v>7320</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>10040</v>
+        <v>26760</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11739,7 +11744,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>10040</v>
+        <v>26760</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11748,14 +11753,14 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>10668</v>
+        <v>7799</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>266.7</v>
+        <v>194.97499999999999</v>
       </c>
       <c r="O6" s="81">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="3:15" ht="32" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -11766,7 +11771,9 @@
       <c r="L7" s="7">
         <v>70</v>
       </c>
-      <c r="M7" s="5"/>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
       <c r="N7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -11786,14 +11793,14 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>10905</v>
+        <v>35486</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>272.625</v>
+        <v>887.15</v>
       </c>
       <c r="O8" s="81">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11802,11 +11809,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-108</v>
+        <v>-186</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-143</v>
+        <v>-183</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -11815,14 +11822,14 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>5595</v>
+        <v>8892</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>139.875</v>
+        <v>222.3</v>
       </c>
       <c r="O9" s="81">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
@@ -11833,25 +11840,25 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>7110</v>
+        <v>43458</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>177.75</v>
+        <v>1086.45</v>
       </c>
       <c r="O10" s="81">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="181" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="180"/>
-      <c r="F11" s="180" t="s">
+      <c r="D11" s="181"/>
+      <c r="F11" s="181" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="180"/>
+      <c r="G11" s="181"/>
       <c r="K11" s="1" t="s">
         <v>7</v>
       </c>
@@ -11859,11 +11866,11 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>66124</v>
+        <v>61610</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1653.1</v>
+        <v>1540.25</v>
       </c>
       <c r="O11" s="81">
         <v>20</v>
@@ -11881,7 +11888,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>3685</v>
+        <v>4103</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11889,15 +11896,15 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>109988</v>
+        <v>164049</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>2749.7</v>
+        <v>4101.2250000000004</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
-        <v>548</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="3:15" ht="18.5" x14ac:dyDescent="0.35">
@@ -11913,7 +11920,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>147400</v>
+        <v>164120</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -11933,170 +11940,337 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K17" s="118" t="s">
         <v>1</v>
       </c>
       <c r="L17" s="120">
         <v>70</v>
       </c>
-      <c r="M17" s="119">
-        <v>11562</v>
-      </c>
+      <c r="M17" s="119"/>
       <c r="N17" s="126">
-        <v>13270</v>
+        <v>8254</v>
       </c>
       <c r="O17" s="127">
         <f>N17-M5</f>
-        <v>3684</v>
-      </c>
-    </row>
-    <row r="18" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>1450</v>
+      </c>
+      <c r="P17">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K18" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L18" s="121">
         <v>70</v>
       </c>
-      <c r="M18" s="5">
-        <v>10770</v>
-      </c>
+      <c r="M18" s="5"/>
       <c r="N18" s="5">
-        <v>14352</v>
+        <v>8818</v>
       </c>
       <c r="O18" s="127">
         <f>N18-M6</f>
-        <v>3684</v>
-      </c>
-    </row>
-    <row r="19" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>1019</v>
+      </c>
+      <c r="P18">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F19" t="s">
+        <v>115</v>
+      </c>
       <c r="K19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="L19" s="121">
         <v>70</v>
       </c>
-      <c r="M19" s="5">
-        <v>14619</v>
-      </c>
+      <c r="M19" s="5"/>
       <c r="N19" s="5">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="O19" s="127">
         <f t="shared" ref="O19:O23" si="1">N19-M7</f>
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="20" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="D20" s="177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="177"/>
+      <c r="F20" s="177"/>
+      <c r="G20" s="177"/>
+      <c r="H20" s="177"/>
       <c r="K20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="121">
         <v>120</v>
       </c>
-      <c r="M20" s="5">
-        <v>19143</v>
-      </c>
+      <c r="M20" s="5"/>
       <c r="N20" s="5">
-        <v>12294</v>
+        <v>38828</v>
       </c>
       <c r="O20" s="127">
         <f t="shared" si="1"/>
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="21" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>3342</v>
+      </c>
+      <c r="P20">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="K21" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L21" s="121">
         <v>120</v>
       </c>
-      <c r="M21" s="5">
-        <v>17100</v>
-      </c>
+      <c r="M21" s="5"/>
       <c r="N21" s="5">
-        <v>6522</v>
+        <v>11781</v>
       </c>
       <c r="O21" s="127">
         <f t="shared" si="1"/>
-        <v>927</v>
-      </c>
-    </row>
-    <row r="22" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>2889</v>
+      </c>
+      <c r="P21">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>70</v>
+      </c>
+      <c r="F22" s="5">
+        <v>9586</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" ref="G22:G28" si="2">F22/40</f>
+        <v>239.65</v>
+      </c>
+      <c r="H22" s="81">
+        <v>186</v>
+      </c>
       <c r="K22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="L22" s="121">
         <v>120</v>
       </c>
-      <c r="M22" s="5">
-        <v>23404</v>
-      </c>
+      <c r="M22" s="5"/>
       <c r="N22" s="5">
-        <v>9539</v>
+        <v>45343</v>
       </c>
       <c r="O22" s="127">
         <f t="shared" si="1"/>
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="23" spans="11:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+        <v>1885</v>
+      </c>
+      <c r="P22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="7">
+        <v>70</v>
+      </c>
+      <c r="F23" s="5">
+        <v>10668</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="2"/>
+        <v>266.7</v>
+      </c>
+      <c r="H23" s="81">
+        <v>103</v>
+      </c>
       <c r="K23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="L23" s="121">
         <v>60</v>
       </c>
-      <c r="M23" s="5">
-        <v>7379</v>
-      </c>
+      <c r="M23" s="5"/>
       <c r="N23" s="5">
-        <v>57991</v>
+        <v>64778</v>
       </c>
       <c r="O23" s="127">
         <f t="shared" si="1"/>
-        <v>-8133</v>
-      </c>
-    </row>
-    <row r="24" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+        <v>3168</v>
+      </c>
+      <c r="P23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="D24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="7">
+        <v>70</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="81">
+        <v>33</v>
+      </c>
       <c r="K24" s="123" t="s">
         <v>74</v>
       </c>
       <c r="L24" s="124"/>
       <c r="M24" s="125">
         <f>SUM(M17:M23)</f>
-        <v>103977</v>
+        <v>0</v>
       </c>
       <c r="N24" s="125">
         <f>SUM(N17:N23)</f>
-        <v>114978</v>
+        <v>177802</v>
       </c>
       <c r="O24" s="122">
         <f>SUM(O17:O23)</f>
-        <v>4990</v>
-      </c>
-    </row>
-    <row r="25" spans="11:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+        <v>13753</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="7">
+        <v>120</v>
+      </c>
+      <c r="F25" s="5">
+        <v>10905</v>
+      </c>
+      <c r="G25" s="6">
+        <f t="shared" si="2"/>
+        <v>272.625</v>
+      </c>
+      <c r="H25" s="81">
+        <v>63</v>
+      </c>
       <c r="K25" s="123" t="s">
         <v>75</v>
       </c>
       <c r="L25" s="124"/>
       <c r="M25" s="125">
         <f>M24/40</f>
-        <v>2599.4250000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="125">
         <f>N24/40</f>
-        <v>2874.45</v>
+        <v>4445.05</v>
       </c>
       <c r="O25" s="122">
         <f>O24/40</f>
-        <v>124.75</v>
+        <v>343.82499999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>120</v>
+      </c>
+      <c r="F26" s="5">
+        <v>5595</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="2"/>
+        <v>139.875</v>
+      </c>
+      <c r="H26" s="81">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="7">
+        <v>120</v>
+      </c>
+      <c r="F27" s="5">
+        <v>7110</v>
+      </c>
+      <c r="G27" s="6">
+        <f t="shared" si="2"/>
+        <v>177.75</v>
+      </c>
+      <c r="H27" s="81">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="7">
+        <v>60</v>
+      </c>
+      <c r="F28" s="5">
+        <v>66124</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="2"/>
+        <v>1653.1</v>
+      </c>
+      <c r="H28" s="81">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" s="8">
+        <f>SUM(F22:F28)</f>
+        <v>109988</v>
+      </c>
+      <c r="G29" s="9">
+        <f>SUM(G22:G28)</f>
+        <v>2749.7</v>
+      </c>
+      <c r="H29" s="9">
+        <f>SUM(H22:H28)</f>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="H3:I3"/>

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A8E1D61-6FF3-4C2E-AF03-329D42A1A8A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F5CE47-3934-4FD3-A2D2-60E091198B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1648,6 +1648,42 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1685,42 +1721,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2279,14 +2279,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="165">
+      <c r="B1" s="152">
         <f ca="1">TODAY()</f>
         <v>46209</v>
       </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2308,10 +2308,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="153" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2344,13 +2344,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="157" t="s">
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="158"/>
+      <c r="Q2" s="170"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2369,8 +2369,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
-      <c r="B3" s="167"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="154"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2401,29 +2401,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="161"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="170"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="172" t="s">
+      <c r="S3" s="157"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="173"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="174"/>
+      <c r="W3" s="160"/>
+      <c r="X3" s="160"/>
+      <c r="Y3" s="161"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
-      <c r="B4" s="168"/>
+      <c r="A4" s="174"/>
+      <c r="B4" s="155"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11128,10 +11128,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="175" t="s">
+      <c r="B132" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="176"/>
+      <c r="C132" s="163"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11395,10 +11395,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="163" t="s">
+      <c r="B136" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="164"/>
+      <c r="C136" s="176"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11489,10 +11489,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="152" t="s">
+      <c r="B137" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="153"/>
+      <c r="C137" s="165"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11584,17 +11584,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F5CE47-3934-4FD3-A2D2-60E091198B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EBD169-ABE2-4E8B-9F1B-87A0FF6947B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2281,7 +2281,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="152">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C1" s="152"/>
       <c r="D1" s="152"/>
@@ -11605,7 +11605,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="C2:P29"/>
+  <dimension ref="C2:Q29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.453125" customWidth="1"/>
@@ -11684,7 +11684,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="E5" s="79">
         <v>183</v>
@@ -11694,12 +11694,12 @@
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>669</v>
+        <v>719</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>669</v>
+        <v>719</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>7440</v>
+        <v>9440</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>26760</v>
+        <v>28760</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11744,7 +11744,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>26760</v>
+        <v>28760</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-186</v>
+        <v>-236</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4103</v>
+        <v>4153</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>164120</v>
+        <v>166120</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -11940,7 +11940,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K17" s="118" t="s">
         <v>1</v>
       </c>
@@ -11958,8 +11958,12 @@
       <c r="P17">
         <v>188</v>
       </c>
-    </row>
-    <row r="18" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q17">
+        <f>N17/40</f>
+        <v>206.35</v>
+      </c>
+    </row>
+    <row r="18" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="K18" s="1" t="s">
         <v>2</v>
       </c>
@@ -11977,8 +11981,12 @@
       <c r="P18">
         <v>109</v>
       </c>
-    </row>
-    <row r="19" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q18">
+        <f t="shared" ref="Q18:Q23" si="1">N18/40</f>
+        <v>220.45</v>
+      </c>
+    </row>
+    <row r="19" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
         <v>115</v>
       </c>
@@ -11993,14 +12001,18 @@
         <v>0</v>
       </c>
       <c r="O19" s="127">
-        <f t="shared" ref="O19:O23" si="1">N19-M7</f>
+        <f t="shared" ref="O19:O23" si="2">N19-M7</f>
         <v>0</v>
       </c>
       <c r="P19">
         <v>33</v>
       </c>
-    </row>
-    <row r="20" spans="4:16" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q19">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D20" s="177" t="s">
         <v>69</v>
       </c>
@@ -12019,14 +12031,18 @@
         <v>38828</v>
       </c>
       <c r="O20" s="127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3342</v>
       </c>
       <c r="P20">
         <v>64</v>
       </c>
-    </row>
-    <row r="21" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q20">
+        <f t="shared" si="1"/>
+        <v>970.7</v>
+      </c>
+    </row>
+    <row r="21" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D21" s="3" t="s">
         <v>0</v>
       </c>
@@ -12053,14 +12069,18 @@
         <v>11781</v>
       </c>
       <c r="O21" s="127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2889</v>
       </c>
       <c r="P21">
         <v>133</v>
       </c>
-    </row>
-    <row r="22" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q21">
+        <f t="shared" si="1"/>
+        <v>294.52499999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D22" s="1" t="s">
         <v>1</v>
       </c>
@@ -12071,7 +12091,7 @@
         <v>9586</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" ref="G22:G28" si="2">F22/40</f>
+        <f t="shared" ref="G22:G28" si="3">F22/40</f>
         <v>239.65</v>
       </c>
       <c r="H22" s="81">
@@ -12088,14 +12108,18 @@
         <v>45343</v>
       </c>
       <c r="O22" s="127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1885</v>
       </c>
       <c r="P22">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q22">
+        <f t="shared" si="1"/>
+        <v>1133.575</v>
+      </c>
+    </row>
+    <row r="23" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D23" s="1" t="s">
         <v>2</v>
       </c>
@@ -12106,7 +12130,7 @@
         <v>10668</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>266.7</v>
       </c>
       <c r="H23" s="81">
@@ -12123,14 +12147,18 @@
         <v>64778</v>
       </c>
       <c r="O23" s="127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3168</v>
       </c>
       <c r="P23">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="4:16" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q23">
+        <f t="shared" si="1"/>
+        <v>1619.45</v>
+      </c>
+    </row>
+    <row r="24" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D24" s="1" t="s">
         <v>3</v>
       </c>
@@ -12139,7 +12167,7 @@
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H24" s="81">
@@ -12162,7 +12190,7 @@
         <v>13753</v>
       </c>
     </row>
-    <row r="25" spans="4:16" ht="24" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
       <c r="D25" s="1" t="s">
         <v>4</v>
       </c>
@@ -12173,7 +12201,7 @@
         <v>10905</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>272.625</v>
       </c>
       <c r="H25" s="81">
@@ -12196,7 +12224,7 @@
         <v>343.82499999999999</v>
       </c>
     </row>
-    <row r="26" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D26" s="1" t="s">
         <v>5</v>
       </c>
@@ -12207,14 +12235,14 @@
         <v>5595</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>139.875</v>
       </c>
       <c r="H26" s="81">
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D27" s="1" t="s">
         <v>6</v>
       </c>
@@ -12225,14 +12253,14 @@
         <v>7110</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>177.75</v>
       </c>
       <c r="H27" s="81">
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D28" s="1" t="s">
         <v>7</v>
       </c>
@@ -12243,14 +12271,14 @@
         <v>66124</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1653.1</v>
       </c>
       <c r="H28" s="81">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="4:16" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="D29" s="1" t="s">
         <v>11</v>
       </c>

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67EBD169-ABE2-4E8B-9F1B-87A0FF6947B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3639D99E-2DB3-4D36-9300-A33B0C1D3F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -372,6 +372,15 @@
   <si>
     <t>Opening July 2026</t>
   </si>
+  <si>
+    <t>Risen Muredky</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Decent Johar Town</t>
+  </si>
 </sst>
 </file>
 
@@ -2281,7 +2290,7 @@
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="152">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C1" s="152"/>
       <c r="D1" s="152"/>
@@ -11684,7 +11693,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="E5" s="79">
         <v>183</v>
@@ -11694,12 +11703,12 @@
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>719</v>
+        <v>759</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>719</v>
+        <v>759</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11724,7 +11733,7 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>9440</v>
+        <v>11040</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
@@ -11736,7 +11745,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>28760</v>
+        <v>30360</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11744,7 +11753,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>28760</v>
+        <v>30360</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11809,7 +11818,7 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-236</v>
+        <v>-276</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
@@ -11888,7 +11897,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4153</v>
+        <v>4193</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11920,7 +11929,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>166120</v>
+        <v>167720</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12519,9 +12528,15 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="81"/>
+      <c r="I12" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="81">
+        <v>13</v>
+      </c>
+      <c r="K12" s="81" t="s">
+        <v>117</v>
+      </c>
       <c r="L12" s="133"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -12529,9 +12544,15 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
+      <c r="I13" s="81" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" s="81">
+        <v>5</v>
+      </c>
+      <c r="K13" s="81" t="s">
+        <v>117</v>
+      </c>
       <c r="L13" s="133"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3639D99E-2DB3-4D36-9300-A33B0C1D3F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731CA978-2D86-407D-A456-3C4CEF3A2C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1657,6 +1657,45 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1691,45 +1730,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2288,14 +2288,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="152">
+      <c r="B1" s="165">
         <f ca="1">TODAY()</f>
         <v>46211</v>
       </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2317,10 +2317,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="166" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2353,13 +2353,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="M2" s="154"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="170"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2378,8 +2378,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="174"/>
-      <c r="B3" s="154"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2410,29 +2410,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="156" t="s">
+      <c r="R3" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="157"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="159" t="s">
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="161"/>
+      <c r="W3" s="173"/>
+      <c r="X3" s="173"/>
+      <c r="Y3" s="174"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="174"/>
-      <c r="B4" s="155"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11137,10 +11137,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="162" t="s">
+      <c r="B132" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="163"/>
+      <c r="C132" s="176"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11404,10 +11404,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="175" t="s">
+      <c r="B136" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="176"/>
+      <c r="C136" s="164"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11498,10 +11498,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="164" t="s">
+      <c r="B137" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="165"/>
+      <c r="C137" s="153"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11593,17 +11593,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -11717,11 +11717,11 @@
         <v>70</v>
       </c>
       <c r="M5" s="5">
-        <v>6804</v>
+        <v>6173</v>
       </c>
       <c r="N5" s="6">
         <f t="shared" ref="N5:N11" si="0">M5/40</f>
-        <v>170.1</v>
+        <v>154.32499999999999</v>
       </c>
       <c r="O5" s="81">
         <v>188</v>
@@ -11762,11 +11762,11 @@
         <v>70</v>
       </c>
       <c r="M6" s="5">
-        <v>7799</v>
+        <v>7443</v>
       </c>
       <c r="N6" s="6">
         <f t="shared" si="0"/>
-        <v>194.97499999999999</v>
+        <v>186.07499999999999</v>
       </c>
       <c r="O6" s="81">
         <v>109</v>
@@ -11802,11 +11802,11 @@
         <v>120</v>
       </c>
       <c r="M8" s="5">
-        <v>35486</v>
+        <v>34701</v>
       </c>
       <c r="N8" s="6">
         <f t="shared" si="0"/>
-        <v>887.15</v>
+        <v>867.52499999999998</v>
       </c>
       <c r="O8" s="81">
         <v>64</v>
@@ -11831,11 +11831,11 @@
         <v>120</v>
       </c>
       <c r="M9" s="5">
-        <v>8892</v>
+        <v>8422</v>
       </c>
       <c r="N9" s="6">
         <f t="shared" si="0"/>
-        <v>222.3</v>
+        <v>210.55</v>
       </c>
       <c r="O9" s="81">
         <v>133</v>
@@ -11849,11 +11849,11 @@
         <v>120</v>
       </c>
       <c r="M10" s="5">
-        <v>43458</v>
+        <v>42523</v>
       </c>
       <c r="N10" s="6">
         <f t="shared" si="0"/>
-        <v>1086.45</v>
+        <v>1063.075</v>
       </c>
       <c r="O10" s="81">
         <v>15</v>
@@ -11875,11 +11875,11 @@
         <v>60</v>
       </c>
       <c r="M11" s="5">
-        <v>61610</v>
+        <v>60810</v>
       </c>
       <c r="N11" s="6">
         <f t="shared" si="0"/>
-        <v>1540.25</v>
+        <v>1520.25</v>
       </c>
       <c r="O11" s="81">
         <v>20</v>
@@ -11905,11 +11905,11 @@
       <c r="L12" s="2"/>
       <c r="M12" s="8">
         <f>SUM(M5:M11)</f>
-        <v>164049</v>
+        <v>160072</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(N5:N11)</f>
-        <v>4101.2250000000004</v>
+        <v>4001.8</v>
       </c>
       <c r="O12" s="9">
         <f>SUM(O5:O11)</f>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="O17" s="127">
         <f>N17-M5</f>
-        <v>1450</v>
+        <v>2081</v>
       </c>
       <c r="P17">
         <v>188</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="O18" s="127">
         <f>N18-M6</f>
-        <v>1019</v>
+        <v>1375</v>
       </c>
       <c r="P18">
         <v>109</v>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="O20" s="127">
         <f t="shared" si="2"/>
-        <v>3342</v>
+        <v>4127</v>
       </c>
       <c r="P20">
         <v>64</v>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="O21" s="127">
         <f t="shared" si="2"/>
-        <v>2889</v>
+        <v>3359</v>
       </c>
       <c r="P21">
         <v>133</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="O22" s="127">
         <f t="shared" si="2"/>
-        <v>1885</v>
+        <v>2820</v>
       </c>
       <c r="P22">
         <v>15</v>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="O23" s="127">
         <f t="shared" si="2"/>
-        <v>3168</v>
+        <v>3968</v>
       </c>
       <c r="P23">
         <v>20</v>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="O24" s="122">
         <f>SUM(O17:O23)</f>
-        <v>13753</v>
+        <v>17730</v>
       </c>
     </row>
     <row r="25" spans="4:17" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="O25" s="122">
         <f>O24/40</f>
-        <v>343.82499999999999</v>
+        <v>443.25</v>
       </c>
     </row>
     <row r="26" spans="4:17" ht="23.5" x14ac:dyDescent="0.55000000000000004">

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731CA978-2D86-407D-A456-3C4CEF3A2C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D6D2B6-F15B-40BA-B77E-1DE4A61FDA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="121">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -381,6 +381,12 @@
   <si>
     <t>Decent Johar Town</t>
   </si>
+  <si>
+    <t xml:space="preserve">Rainbiw Wapda Town </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -1657,6 +1663,42 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1694,42 +1736,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2288,14 +2294,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="165">
+      <c r="B1" s="152">
         <f ca="1">TODAY()</f>
-        <v>46211</v>
-      </c>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
+        <v>46212</v>
+      </c>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2317,10 +2323,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="174" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="166" t="s">
+      <c r="B2" s="153" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2353,13 +2359,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="154"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="157" t="s">
+      <c r="M2" s="166"/>
+      <c r="N2" s="167"/>
+      <c r="O2" s="168"/>
+      <c r="P2" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="158"/>
+      <c r="Q2" s="170"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2378,8 +2384,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="162"/>
-      <c r="B3" s="167"/>
+      <c r="A3" s="174"/>
+      <c r="B3" s="154"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2410,29 +2416,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="159" t="s">
+      <c r="M3" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="160"/>
-      <c r="O3" s="161"/>
+      <c r="N3" s="172"/>
+      <c r="O3" s="173"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="169" t="s">
+      <c r="R3" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="170"/>
-      <c r="T3" s="170"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="172" t="s">
+      <c r="S3" s="157"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="159" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="173"/>
-      <c r="X3" s="173"/>
-      <c r="Y3" s="174"/>
+      <c r="W3" s="160"/>
+      <c r="X3" s="160"/>
+      <c r="Y3" s="161"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="162"/>
-      <c r="B4" s="168"/>
+      <c r="A4" s="174"/>
+      <c r="B4" s="155"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -11137,10 +11143,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="175" t="s">
+      <c r="B132" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="176"/>
+      <c r="C132" s="163"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11404,10 +11410,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="163" t="s">
+      <c r="B136" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="164"/>
+      <c r="C136" s="176"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11498,10 +11504,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="152" t="s">
+      <c r="B137" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="153"/>
+      <c r="C137" s="165"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11593,17 +11599,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -12560,9 +12566,15 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
+      <c r="I14" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="81">
+        <v>8</v>
+      </c>
+      <c r="K14" s="81" t="s">
+        <v>117</v>
+      </c>
       <c r="L14" s="133"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
@@ -12570,9 +12582,15 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="81"/>
+      <c r="I15" s="81" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15" s="81">
+        <v>10</v>
+      </c>
+      <c r="K15" s="81" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>

--- a/july 2026/LMT Orders.xlsx
+++ b/july 2026/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D6D2B6-F15B-40BA-B77E-1DE4A61FDA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D200657-5FB3-444F-9B0E-E17801608C25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="127">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -385,7 +385,25 @@
     <t xml:space="preserve">Rainbiw Wapda Town </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">Decent Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainbow Wapda Town </t>
+  </si>
+  <si>
+    <t>Jalal Sons Izmir Town</t>
+  </si>
+  <si>
+    <t>Risen Thoker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zohra Mart </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Rehmat </t>
+  </si>
+  <si>
+    <t>Raheem Store EME</t>
   </si>
 </sst>
 </file>
@@ -1663,6 +1681,45 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1697,45 +1754,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2294,14 +2312,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="152">
+      <c r="B1" s="165">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
-      </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="152"/>
+        <v>46213</v>
+      </c>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2323,10 +2341,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="153" t="s">
+      <c r="B2" s="166" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2359,13 +2377,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="166"/>
-      <c r="N2" s="167"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="169" t="s">
+      <c r="M2" s="154"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="157" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="170"/>
+      <c r="Q2" s="158"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2384,8 +2402,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="174"/>
-      <c r="B3" s="154"/>
+      <c r="A3" s="162"/>
+      <c r="B3" s="167"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2416,29 +2434,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="171" t="s">
+      <c r="M3" s="159" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="172"/>
-      <c r="O3" s="173"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="161"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="156" t="s">
+      <c r="R3" s="169" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="157"/>
-      <c r="T3" s="157"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="159" t="s">
+      <c r="S3" s="170"/>
+      <c r="T3" s="170"/>
+      <c r="U3" s="171"/>
+      <c r="V3" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="161"/>
+      <c r="W3" s="173"/>
+      <c r="X3" s="173"/>
+      <c r="Y3" s="174"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="174"/>
-      <c r="B4" s="155"/>
+      <c r="A4" s="162"/>
+      <c r="B4" s="168"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -3582,26 +3600,26 @@
       <c r="B18" s="47">
         <v>14</v>
       </c>
-      <c r="C18" s="145" t="s">
+      <c r="C18" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="146"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="148"/>
-      <c r="G18" s="149">
+      <c r="D18" s="74"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="50">
         <v>120</v>
       </c>
-      <c r="H18" s="147">
+      <c r="H18" s="75">
         <v>80</v>
       </c>
-      <c r="I18" s="150"/>
-      <c r="J18" s="149">
+      <c r="I18" s="49"/>
+      <c r="J18" s="50">
         <v>40</v>
       </c>
-      <c r="K18" s="147">
+      <c r="K18" s="75">
         <v>40</v>
       </c>
-      <c r="L18" s="148">
+      <c r="L18" s="76">
         <v>120</v>
       </c>
       <c r="M18" s="48">
@@ -3664,22 +3682,22 @@
       <c r="B19" s="47">
         <v>15</v>
       </c>
-      <c r="C19" s="145" t="s">
+      <c r="C19" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="146"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="148"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="149">
+      <c r="D19" s="74"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="50">
         <v>120</v>
       </c>
-      <c r="K19" s="147">
+      <c r="K19" s="75">
         <v>120</v>
       </c>
-      <c r="L19" s="148">
+      <c r="L19" s="76">
         <v>120</v>
       </c>
       <c r="M19" s="48">
@@ -3742,22 +3760,22 @@
       <c r="B20" s="47">
         <v>16</v>
       </c>
-      <c r="C20" s="145" t="s">
+      <c r="C20" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="146"/>
-      <c r="E20" s="147"/>
-      <c r="F20" s="148"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="147"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="149">
+      <c r="D20" s="74"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="50">
         <v>240</v>
       </c>
-      <c r="K20" s="147">
+      <c r="K20" s="75">
         <v>240</v>
       </c>
-      <c r="L20" s="148">
+      <c r="L20" s="76">
         <v>240</v>
       </c>
       <c r="M20" s="48">
@@ -3820,26 +3838,26 @@
       <c r="B21" s="47">
         <v>17</v>
       </c>
-      <c r="C21" s="145" t="s">
+      <c r="C21" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="146"/>
-      <c r="E21" s="147"/>
-      <c r="F21" s="148"/>
-      <c r="G21" s="149">
+      <c r="D21" s="74"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="50">
         <v>40</v>
       </c>
-      <c r="H21" s="147">
+      <c r="H21" s="75">
         <v>40</v>
       </c>
-      <c r="I21" s="150"/>
-      <c r="J21" s="149">
+      <c r="I21" s="49"/>
+      <c r="J21" s="50">
         <v>40</v>
       </c>
-      <c r="K21" s="147">
+      <c r="K21" s="75">
         <v>40</v>
       </c>
-      <c r="L21" s="148">
+      <c r="L21" s="76">
         <v>40</v>
       </c>
       <c r="M21" s="48">
@@ -4134,23 +4152,33 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="78"/>
+      <c r="A25" s="78">
+        <v>46212</v>
+      </c>
       <c r="B25" s="47">
         <v>21</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="76"/>
+      <c r="C25" s="145" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="146"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="148"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="150"/>
+      <c r="J25" s="149">
+        <v>40</v>
+      </c>
+      <c r="K25" s="147">
+        <v>80</v>
+      </c>
+      <c r="L25" s="148">
+        <v>80</v>
+      </c>
       <c r="M25" s="48">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N25" s="39">
         <f t="shared" si="18"/>
@@ -4166,7 +4194,7 @@
       </c>
       <c r="Q25" s="40">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R25" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4202,23 +4230,37 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="78"/>
+      <c r="A26" s="78">
+        <v>46212</v>
+      </c>
       <c r="B26" s="47">
         <v>22</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="76"/>
+      <c r="C26" s="145" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="146"/>
+      <c r="E26" s="147"/>
+      <c r="F26" s="148"/>
+      <c r="G26" s="149">
+        <v>80</v>
+      </c>
+      <c r="H26" s="147">
+        <v>80</v>
+      </c>
+      <c r="I26" s="150"/>
+      <c r="J26" s="149">
+        <v>80</v>
+      </c>
+      <c r="K26" s="147">
+        <v>80</v>
+      </c>
+      <c r="L26" s="148">
+        <v>80</v>
+      </c>
       <c r="M26" s="48">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N26" s="39">
         <f t="shared" si="18"/>
@@ -4230,11 +4272,11 @@
       </c>
       <c r="P26" s="73">
         <f t="shared" si="48"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="40">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R26" s="51" t="e">
         <f t="shared" si="4"/>
@@ -4270,23 +4312,33 @@
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="78"/>
+      <c r="A27" s="78">
+        <v>46212</v>
+      </c>
       <c r="B27" s="47">
         <v>23</v>
       </c>
-      <c r="C27" s="57"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="75"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="76"/>
+      <c r="C27" s="145" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="146"/>
+      <c r="E27" s="147"/>
+      <c r="F27" s="148"/>
+      <c r="G27" s="149"/>
+      <c r="H27" s="147"/>
+      <c r="I27" s="150"/>
+      <c r="J27" s="149">
+        <v>40</v>
+      </c>
+      <c r="K27" s="147">
+        <v>120</v>
+      </c>
+      <c r="L27" s="148">
+        <v>160</v>
+      </c>
       <c r="M27" s="48">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N27" s="39">
         <f t="shared" si="18"/>
@@ -4302,7 +4354,7 @@
       </c>
       <c r="Q27" s="40">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R27" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11143,10 +11195,10 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" s="78"/>
-      <c r="B132" s="162" t="s">
+      <c r="B132" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C132" s="163"/>
+      <c r="C132" s="176"/>
       <c r="D132" s="88">
         <f t="shared" ref="D132:L132" si="104">SUM(D6:D60)</f>
         <v>0</v>
@@ -11161,11 +11213,11 @@
       </c>
       <c r="G132" s="88">
         <f t="shared" si="104"/>
-        <v>878</v>
+        <v>958</v>
       </c>
       <c r="H132" s="88">
         <f t="shared" si="104"/>
-        <v>877</v>
+        <v>957</v>
       </c>
       <c r="I132" s="88">
         <f t="shared" si="104"/>
@@ -11173,19 +11225,19 @@
       </c>
       <c r="J132" s="88">
         <f t="shared" si="104"/>
-        <v>1319</v>
+        <v>1479</v>
       </c>
       <c r="K132" s="88">
         <f t="shared" si="104"/>
-        <v>1038</v>
+        <v>1318</v>
       </c>
       <c r="L132" s="88">
         <f t="shared" si="104"/>
-        <v>1398</v>
+        <v>1718</v>
       </c>
       <c r="M132" s="48">
         <f t="shared" ref="M132:M135" si="105">SUM(D132:L132)/40</f>
-        <v>137.75</v>
+        <v>160.75</v>
       </c>
       <c r="N132" s="39">
         <f t="shared" si="18"/>
@@ -11197,11 +11249,11 @@
       </c>
       <c r="P132" s="73">
         <f t="shared" ref="P132:P136" si="106">SUM(G132:I132)/20</f>
-        <v>87.75</v>
+        <v>95.75</v>
       </c>
       <c r="Q132" s="40">
         <f t="shared" ref="Q132:Q136" si="107">SUM(J132:L132)/20</f>
-        <v>187.75</v>
+        <v>225.75</v>
       </c>
       <c r="R132" s="51" t="e">
         <f t="shared" si="4"/>
@@ -11410,10 +11462,10 @@
       </c>
     </row>
     <row r="136" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="175" t="s">
+      <c r="B136" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="C136" s="176"/>
+      <c r="C136" s="164"/>
       <c r="D136" s="87">
         <f>SUM(D134:D135)</f>
         <v>0</v>
@@ -11504,10 +11556,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="164" t="s">
+      <c r="B137" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="C137" s="165"/>
+      <c r="C137" s="153"/>
       <c r="D137" s="89">
         <f>SUM(D132,D136)</f>
         <v>0</v>
@@ -11522,11 +11574,11 @@
       </c>
       <c r="G137" s="89">
         <f t="shared" si="112"/>
-        <v>878</v>
+        <v>958</v>
       </c>
       <c r="H137" s="89">
         <f t="shared" si="112"/>
-        <v>877</v>
+        <v>957</v>
       </c>
       <c r="I137" s="89">
         <f t="shared" si="112"/>
@@ -11534,19 +11586,19 @@
       </c>
       <c r="J137" s="89">
         <f t="shared" si="112"/>
-        <v>1319</v>
+        <v>1479</v>
       </c>
       <c r="K137" s="89">
         <f t="shared" si="112"/>
-        <v>1038</v>
+        <v>1318</v>
       </c>
       <c r="L137" s="89">
         <f t="shared" si="112"/>
-        <v>1398</v>
+        <v>1718</v>
       </c>
       <c r="M137" s="60">
         <f t="shared" si="0"/>
-        <v>137.75</v>
+        <v>160.75</v>
       </c>
       <c r="N137" s="63">
         <f>SUM(N5:N136)</f>
@@ -11558,11 +11610,11 @@
       </c>
       <c r="P137" s="62">
         <f t="shared" si="113"/>
-        <v>179.5</v>
+        <v>195.5</v>
       </c>
       <c r="Q137" s="64">
         <f t="shared" si="113"/>
-        <v>381.5</v>
+        <v>457.5</v>
       </c>
       <c r="R137" s="65" t="e">
         <f t="shared" si="113"/>
@@ -11599,22 +11651,23 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B132:C132"/>
     <mergeCell ref="B137:C137"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B132:C132"/>
   </mergeCells>
   <conditionalFormatting sqref="C45:C59">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11699,22 +11752,22 @@
         <v>51</v>
       </c>
       <c r="D5" s="92">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="E5" s="79">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="F5" s="79">
         <v>300</v>
       </c>
       <c r="G5" s="106">
         <f>SUM(D5:F5)</f>
-        <v>759</v>
+        <v>856</v>
       </c>
       <c r="H5" s="99"/>
       <c r="I5" s="100">
         <f>G5-H5</f>
-        <v>759</v>
+        <v>856</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>1</v>
@@ -11739,11 +11792,11 @@
       </c>
       <c r="D6" s="108">
         <f>D5*40</f>
-        <v>11040</v>
+        <v>14000</v>
       </c>
       <c r="E6" s="109">
         <f>E5*40</f>
-        <v>7320</v>
+        <v>8240</v>
       </c>
       <c r="F6" s="109">
         <f>F5*40</f>
@@ -11751,7 +11804,7 @@
       </c>
       <c r="G6" s="110">
         <f>SUM(D6:F6)</f>
-        <v>30360</v>
+        <v>34240</v>
       </c>
       <c r="H6" s="101">
         <f>H5*40</f>
@@ -11759,7 +11812,7 @@
       </c>
       <c r="I6" s="102">
         <f>G6-H6</f>
-        <v>30360</v>
+        <v>34240</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>2</v>
@@ -11824,11 +11877,11 @@
       </c>
       <c r="D9" s="111">
         <f>D8-D5</f>
-        <v>-276</v>
+        <v>-350</v>
       </c>
       <c r="E9" s="111">
         <f>E8-E5</f>
-        <v>-183</v>
+        <v>-206</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>5</v>
@@ -11903,7 +11956,7 @@
       </c>
       <c r="G12" s="95">
         <f>D12+G5</f>
-        <v>4193</v>
+        <v>4290</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>11</v>
@@ -11935,7 +11988,7 @@
       </c>
       <c r="G13" s="95">
         <f>G12*40</f>
-        <v>167720</v>
+        <v>171600</v>
       </c>
     </row>
     <row r="16" spans="3:15" ht="24" thickBot="1" x14ac:dyDescent="0.6">
@@ -12556,8 +12609,8 @@
       <c r="J13" s="81">
         <v>5</v>
       </c>
-      <c r="K13" s="81" t="s">
-        <v>117</v>
+      <c r="K13" s="139" t="s">
+        <v>100</v>
       </c>
       <c r="L13" s="133"/>
     </row>
@@ -12572,8 +12625,8 @@
       <c r="J14" s="81">
         <v>8</v>
       </c>
-      <c r="K14" s="81" t="s">
-        <v>117</v>
+      <c r="K14" s="139" t="s">
+        <v>100</v>
       </c>
       <c r="L14" s="133"/>
     </row>
@@ -12588,8 +12641,8 @@
       <c r="J15" s="81">
         <v>10</v>
       </c>
-      <c r="K15" s="81" t="s">
-        <v>120</v>
+      <c r="K15" s="139" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
@@ -12597,9 +12650,15 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="81"/>
+      <c r="I16" s="81" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="81">
+        <v>5</v>
+      </c>
+      <c r="K16" s="81" t="s">
+        <v>110</v>
+      </c>
       <c r="L16" s="134"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -12607,41 +12666,71 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
+      <c r="I17" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="81">
+        <v>4</v>
+      </c>
+      <c r="K17" s="81" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="81"/>
+      <c r="I18" s="81" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" s="81">
+        <v>9</v>
+      </c>
+      <c r="K18" s="81" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="83"/>
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
       <c r="D19" s="83"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="81"/>
-      <c r="K19" s="81"/>
+      <c r="I19" s="81" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="81">
+        <v>6</v>
+      </c>
+      <c r="K19" s="81" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="84"/>
       <c r="B20" s="85"/>
       <c r="C20" s="85"/>
       <c r="D20" s="86"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
+      <c r="I20" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="J20" s="81">
+        <v>30</v>
+      </c>
+      <c r="K20" s="81" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="I21" s="81"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="81"/>
+      <c r="I21" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="81">
+        <v>22</v>
+      </c>
+      <c r="K21" s="81" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="I22" s="81"/>
